--- a/data/credit_bond_all_2026-08-27.xlsx
+++ b/data/credit_bond_all_2026-08-27.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-08-27" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-08-28" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-08-27</t>
+          <t>数据来源：DM    2026-08-28</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>1.6000/1.6000</t>
+          <t>1.6100/1.6000</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.8945</t>
+          <t>1.8780</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.90</t>
+          <t>D+ 6.32</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.6872</t>
+          <t>1.6864</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C- 20.85</t>
+          <t>C- 22.20</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>2.0200/1.9700</t>
+          <t>--/1.9300</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B- 45.77</t>
+          <t>B- 47.29</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.7758</t>
+          <t>1.7727</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C 25.67</t>
+          <t>C- 24.27</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>2.0600/2.0500</t>
+          <t>--/2.0450</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
@@ -3019,7 +3019,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>A- 61.10</t>
+          <t>B+ 59.04</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>1.7500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 40.69</t>
+          <t>B- 38.66</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>A- 61.01</t>
+          <t>A- 64.48</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.57</t>
+          <t>C+ 33.33</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.5200</t>
+          <t>--/1.5200</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 36.19</t>
+          <t>B- 35.81</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>1.9350/1.9325</t>
+          <t>1.9400/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>B- 45.54</t>
+          <t>B- 44.10</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>1.7850/--</t>
+          <t>1.8100/--</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>B- 40.69</t>
+          <t>B- 38.66</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>--/1.4500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
@@ -5259,8 +5259,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="H23" s="4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>54.49</v>
+      </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
           <t>1.97</t>
@@ -5278,7 +5282,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>2.0119</t>
+          <t>2.0186</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -5509,7 +5513,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.5200</t>
+          <t>--/1.5200</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -5519,7 +5523,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B- 36.19</t>
+          <t>B- 35.81</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5732,7 +5736,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7460</t>
+          <t>1.7522</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5975,7 +5979,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>A- 61.10</t>
+          <t>B+ 59.04</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6190,12 +6194,12 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.7738</t>
+          <t>1.7779</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>1.8000/1.7600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -6205,7 +6209,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>C 29.38</t>
+          <t>C 29.88</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6418,12 +6422,12 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.9998</t>
+          <t>1.9958</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>1.9900/1.9800</t>
+          <t>2.0200/--</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -6433,7 +6437,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C 29.38</t>
+          <t>C 29.88</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6655,7 +6659,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>1.8000/1.5842</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
@@ -6665,7 +6669,7 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.69</t>
+          <t>B- 36.16</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
@@ -7055,7 +7059,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -7111,7 +7115,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.44</t>
+          <t>C 28.70</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7279,7 +7283,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -7301,8 +7305,12 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
+      <c r="H32" s="4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>56.49</v>
+      </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
           <t>1.84</t>
@@ -7325,7 +7333,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/1.8200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -7498,17 +7506,17 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26济运01</t>
+          <t>26济旅04</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>283795.SH</t>
+          <t>283750.SH</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
@@ -7517,49 +7525,53 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.23</v>
+        <v>5.0</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.20</t>
-        </is>
-      </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
+          <t>1.90 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>73.85</v>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>24济运04</t>
+          <t>26济旅03</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>4.64Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>2.0581</t>
+          <t>2.1766</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>2.0600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>济宁市城运集团有限公司</t>
+          <t>济南文旅发展集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.44</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7579,19 +7591,19 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>2.24%~2.34%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -7602,17 +7614,17 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>山东省-济宁市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金0.23亿元,扣除发行费用后拟用于偿还公司债券本金或置换偿还到期公司债券本金的自有资金[23任兴03,23任兴04,23任城04]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务,包括公司债券本金和其他有息债务[23济旅02]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,恒泰长财证券有限责任公司,长城证券股份有限公司,申港证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
@@ -7633,7 +7645,7 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>济宁市城运集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>济南文旅发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
@@ -7643,10 +7655,14 @@
       </c>
       <c r="AJ33" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
-        </is>
-      </c>
-      <c r="AK33" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL33" s="3" t="inlineStr">
         <is>
           <t/>
@@ -7659,7 +7675,7 @@
       </c>
       <c r="AN33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO33" s="3" t="inlineStr">
@@ -7669,7 +7685,7 @@
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
@@ -7679,17 +7695,17 @@
       </c>
       <c r="AR33" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS33" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
@@ -7722,7 +7738,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26泗洪01</t>
+          <t>26北仑现代PPN001</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7730,18 +7746,14 @@
           <t>08-27 18:00</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>283814.SH</t>
-        </is>
-      </c>
+      <c r="C34" s="3"/>
       <c r="D34" s="3" t="inlineStr">
         <is>
           <t>3+2</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.0</v>
+        <v>8.0</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="inlineStr">
@@ -7753,14 +7765,22 @@
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>24宁现02</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>226D+2.00Y</t>
+        </is>
+      </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>--</t>
+          <t>1.5501</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -7770,12 +7790,12 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>泗洪县宏源公有资产经营集团有限公司</t>
+          <t>宁波市北仑区现代服务业发展集团有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>D 4.76</t>
+          <t>C- 10.80</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7785,7 +7805,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7802,39 +7822,39 @@
       <c r="V34" s="3"/>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行总额不超过人民币10亿元(含10亿元),发行人在扣除发行费用后,全部用于偿还回售的公司债券本金[23泗洪01]</t>
+          <t>发行人本次债务融资工具募集资金拟用于偿还23北仑现代PPN001债券本金；发行人已通过银行借款偿还到期的23北仑现代PPN001，本期募集资金用途用于偿还该笔银行专项借款[23北仑现代PPN001]</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
+          <t>宁波银行股份有限公司,杭州银行股份有限公司,兴业银行股份有限公司,徽商银行股份有限公司,中信银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
       <c r="AE34" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF34" s="3" t="inlineStr">
@@ -7844,12 +7864,12 @@
       </c>
       <c r="AG34" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>泗洪县宏源公有资产经营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>宁波市北仑区现代服务业发展集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7865,7 +7885,7 @@
       <c r="AK34" s="3"/>
       <c r="AL34" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM34" s="3" t="inlineStr">
@@ -7880,12 +7900,12 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ34" s="3" t="inlineStr">
@@ -7895,17 +7915,17 @@
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -7938,7 +7958,7 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26济旅04</t>
+          <t>26天能控股PPN002(科创债)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -7948,12 +7968,12 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>283750.SH</t>
+          <t>032680479.IB</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1+1</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
@@ -7962,29 +7982,29 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.70</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26济旅03</t>
+          <t>26天能控股PPN001(科创债)</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>4.64Y</t>
+          <t>201D</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>2.1745</t>
+          <t>1.5476</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -7994,7 +8014,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>济南文旅发展集团有限公司</t>
+          <t>天能控股集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
@@ -8009,7 +8029,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8019,19 +8039,19 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>2.24%~2.34%</t>
+          <t>1.49%~1.53%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8042,38 +8062,38 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务,包括公司债券本金和其他有息债务[23济旅02]</t>
+          <t>本期定向科技创新债券基础发行规模5亿元，发行金额上限为10亿元。本期募集资金拟用于归还存量银行贷款。</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>中信证券股份有限公司,交通银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司,渤海银行股份有限公司,南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>济南文旅发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>天能控股集团有限公司2026年度第二期定向科技创新债券</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8083,17 +8103,13 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK35" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2028-08-28</t>
+        </is>
+      </c>
+      <c r="AK35" s="3"/>
       <c r="AL35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM35" s="3" t="inlineStr">
@@ -8103,42 +8119,38 @@
       </c>
       <c r="AN35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP35" s="3"/>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>电力设备制造</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>其他电力设备</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>电源设备</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2027-08-28</t>
         </is>
       </c>
       <c r="AV35" s="3" t="inlineStr">
@@ -8148,7 +8160,7 @@
       </c>
       <c r="AW35" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX35" s="3" t="inlineStr">
@@ -8166,7 +8178,7 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26医产K1</t>
+          <t>26南通融通PPN001</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -8174,58 +8186,58 @@
           <t>08-27 18:00</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>520443.SZ</t>
-        </is>
-      </c>
+      <c r="C36" s="3"/>
       <c r="D36" s="3" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3.0</v>
+        <v>1.19</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.60 ~ 2.10</t>
         </is>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26君实生物MTN003(科创债)</t>
+          <t>26融通01</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>2.98Y</t>
+          <t>2.67Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>2.7236</t>
+          <t>1.7528</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/2.7100</t>
+          <t>1.7850/--</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>四川生物医药产业集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="P36" s="3"/>
+          <t>南通融通控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>S- 87.05</t>
+        </is>
+      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -8233,7 +8245,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8243,17 +8255,21 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X36" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>1.78%~1.88%</t>
+        </is>
+      </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -8262,23 +8278,23 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>江苏省-南通市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不低于2.10亿元用于股权投资;不低于0.71亿元用于认购基金份额;剩余部分用于偿还有息债务。</t>
+          <t>本期定向债务融资工具发行金额1.19亿元,募集资金用于偿还发行人存量债务融资工具本金[24南通融通PPN001]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
+          <t>江苏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8288,12 +8304,12 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>四川生物医药产业集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)(用于生物医药)</t>
+          <t>南通融通控股集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8303,13 +8319,13 @@
       </c>
       <c r="AJ36" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8319,33 +8335,37 @@
       </c>
       <c r="AN36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP36" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8378,7 +8398,7 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26北仑现代PPN001</t>
+          <t>26建湖城投PPN003</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -8389,38 +8409,38 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>8.0</v>
+        <v>4.2</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.60 ~ 2.70</t>
         </is>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>24宁现02</t>
+          <t>26建湖城投PPN001</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>226D+2.00Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.5478</t>
+          <t>2.2025</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -8430,12 +8450,12 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>宁波市北仑区现代服务业发展集团有限公司</t>
+          <t>建湖县城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C- 10.80</t>
+          <t>D 4.67</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8462,33 +8482,33 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.03%~2.13%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>江苏省-盐城市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>发行人本次债务融资工具募集资金拟用于偿还23北仑现代PPN001债券本金；发行人已通过银行借款偿还到期的23北仑现代PPN001，本期募集资金用途用于偿还该笔银行专项借款[23北仑现代PPN001]</t>
+          <t>本次拟发行4.2亿元定向债务融资工具,拟全部用于偿还发行人债务融资工具。[24建湖城投PPN001,24建湖城投PPN002]</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,杭州银行股份有限公司,兴业银行股份有限公司,徽商银行股份有限公司,中信银行股份有限公司,北京银行股份有限公司</t>
+          <t>南京银行股份有限公司,中信证券股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8509,7 +8529,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>宁波市北仑区现代服务业发展集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>建湖县城市建设投资集团有限公司2026年度第三期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8545,32 +8565,32 @@
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV37" s="3" t="inlineStr">
@@ -8580,7 +8600,7 @@
       </c>
       <c r="AW37" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX37" s="3" t="inlineStr">
@@ -8593,12 +8613,14 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ37" s="3"/>
+      <c r="AZ37" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26天能控股PPN002(科创债)</t>
+          <t>26东港投资PPN001</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -8606,60 +8628,56 @@
           <t>08-27 18:00</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>032680479.IB</t>
-        </is>
-      </c>
+      <c r="C38" s="3"/>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>1+1</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>26天能控股PPN001(科创债)</t>
+          <t>26东港02</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>201D</t>
+          <t>2.96Y+2.00Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.5476</t>
+          <t>1.8000</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7300</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>天能控股集团有限公司</t>
+          <t>东港投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B- 35.32</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8669,7 +8687,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8686,33 +8704,33 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t>1.49%~1.53%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>浙江省-舟山市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期定向科技创新债券基础发行规模5亿元，发行金额上限为10亿元。本期募集资金拟用于归还存量银行贷款。</t>
+          <t>发行人本期定向债务融资工具募集资金中,3.00亿元拟用于偿还21东港投资PPN001的本金[21东港投资PPN001]</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,交通银行股份有限公司,中国邮政储蓄银行股份有限公司,浙商银行股份有限公司,渤海银行股份有限公司,南京银行股份有限公司</t>
+          <t>杭州银行股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
@@ -8723,7 +8741,7 @@
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
@@ -8733,7 +8751,7 @@
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>天能控股集团有限公司2026年度第二期定向科技创新债券</t>
+          <t>东港投资发展集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
@@ -8743,7 +8761,7 @@
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2028-08-28</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
@@ -8764,33 +8782,37 @@
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP38" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>电力设备制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>电源设备</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
         <is>
-          <t>2027-08-28</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AV38" s="3" t="inlineStr">
@@ -8818,64 +8840,68 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26南通融通PPN001</t>
+          <t>26新乡Y1</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
-        </is>
-      </c>
-      <c r="C39" s="3"/>
+          <t>08-27 19:00</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>283836.SH</t>
+        </is>
+      </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1.19</v>
+        <v>4.0</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.10</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>26融通01</t>
+          <t>26新乡投资PPN002</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>2.67Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1.7523</t>
+          <t>1.8637</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>1.7850/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>南通融通控股集团有限公司</t>
+          <t>新乡投资集团有限公司</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>S- 87.05</t>
+          <t>C 27.67</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -8885,7 +8911,7 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
@@ -8895,46 +8921,42 @@
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t>1.78%~1.88%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X39" s="3"/>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南通市</t>
+          <t>河南省-新乡市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期定向债务融资工具发行金额1.19亿元,募集资金用于偿还发行人存量债务融资工具本金[24南通融通PPN001]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还即将到期公司债券本金。[23 新乡03]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>江苏银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -8944,12 +8966,12 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>南通融通控股集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>新乡投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -8959,25 +8981,25 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AM39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>城投</t>
@@ -8990,22 +9012,22 @@
       </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU39" s="3" t="inlineStr">
@@ -9020,12 +9042,12 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY39" s="3" t="inlineStr">
@@ -9038,49 +9060,53 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26建湖城投PPN003</t>
+          <t>26临开Y1</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
-        </is>
-      </c>
-      <c r="C40" s="3"/>
+          <t>08-27 19:00</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>283847.SH</t>
+        </is>
+      </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>4.2</v>
+        <v>15.0</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.70</t>
+          <t>1.80 ~ 2.60</t>
         </is>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>26建湖城投PPN001</t>
+          <t>25临开Y1</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>1.65Y+N</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>2.2025</t>
+          <t>1.8062</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -9090,12 +9116,12 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>建湖县城市建设投资集团有限公司</t>
+          <t>杭州临平开发投资集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>D 4.06</t>
+          <t>C- 11.54</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9105,7 +9131,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9122,39 +9148,35 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t>2.03%~2.13%</t>
-        </is>
-      </c>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X40" s="3"/>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>江苏省-盐城市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>本次拟发行4.2亿元定向债务融资工具,拟全部用于偿还发行人债务融资工具。[24建湖城投PPN001,24建湖城投PPN002]</t>
+          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还公司债券本金。[23临开Y1]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司,中信证券股份有限公司</t>
+          <t>国金证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9164,12 +9186,12 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>建湖县城市建设投资集团有限公司2026年度第三期定向债务融资工具</t>
+          <t>杭州临平开发投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
@@ -9185,7 +9207,7 @@
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -9200,27 +9222,27 @@
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP40" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
@@ -9240,7 +9262,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9253,14 +9275,12 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ40" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ40" s="3"/>
     </row>
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26东港投资PPN001</t>
+          <t>26中远海运MTN007(科创债)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9268,56 +9288,62 @@
           <t>08-27 18:00</t>
         </is>
       </c>
-      <c r="C41" s="3"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>102683436.IB</t>
+        </is>
+      </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>15Y</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F41" s="3"/>
+        <v>50.0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>50.0</v>
+      </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>2.00 ~ 2.30</t>
         </is>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26东港02</t>
+          <t>24中远海运MTN001</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+2.00Y</t>
+          <t>12.96Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.8028</t>
+          <t>2.1444</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/1.7300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>东港投资发展集团有限公司</t>
+          <t>中国远洋海运集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 35.32</t>
+          <t>C- 20.86</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9327,7 +9353,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9344,44 +9370,44 @@
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>2.13%~2.23%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>浙江省-舟山市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具募集资金中,3.00亿元拟用于偿还21东港投资PPN001的本金[21东港投资PPN001]</t>
+          <t>发行人拟将本次募集资金50亿元用于偿还发行人本部及合并报表范围内子公司的有息债务及支付船舶建造款</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,国泰海通证券股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG41" s="3" t="inlineStr">
@@ -9391,17 +9417,17 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>东港投资发展集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>中国远洋海运集团有限公司2026年度第七期科技创新债券</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2041-08-28</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
@@ -9412,7 +9438,7 @@
       </c>
       <c r="AM41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AN41" s="3" t="inlineStr">
@@ -9422,37 +9448,37 @@
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>交通运输</t>
         </is>
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AU41" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV41" s="3" t="inlineStr">
@@ -9462,7 +9488,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9480,7 +9506,7 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26京城01</t>
+          <t>26新凤鸣控SCP005</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -9490,58 +9516,60 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>283799.SH</t>
+          <t>012682168.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F42" s="3"/>
+        <v>2.0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>2.0</v>
+      </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.45 ~ 1.65</t>
         </is>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>25京城01</t>
+          <t>26新凤鸣控SCP004</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>1.79Y</t>
+          <t>180D</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1.9253</t>
+          <t>1.6342</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>1.9600/1.9300</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>北京城建投资发展股份有限公司</t>
+          <t>新凤鸣控股集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B 51.22</t>
+          <t>C+ 33.33</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9551,7 +9579,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>08-27 16:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9561,77 +9589,77 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U42" s="3"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X42" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>1.65%~1.69%</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-嘉兴市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金4亿元拟全部用于偿还公司债券本金[24北城01]</t>
+          <t>本期发行超短期融资券2亿元,用于偿还发行人到期的债务融资工具本金。[25新凤鸣控SCP004]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>中信银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>北京城建投资发展股份有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>新凤鸣控股集团有限公司2026年度第五期超短期融资券</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK42" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2027-05-25</t>
+        </is>
+      </c>
+      <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
@@ -9641,7 +9669,7 @@
       </c>
       <c r="AN42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO42" s="3" t="inlineStr">
@@ -9649,29 +9677,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
+      <c r="AP42" s="3"/>
       <c r="AQ42" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>化工制造</t>
         </is>
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>综合地产开发</t>
+          <t>化学制品</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>化学纤维</t>
         </is>
       </c>
       <c r="AU42" s="3" t="inlineStr">
@@ -9704,53 +9728,57 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26新乡Y1</t>
+          <t>26苏农01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>283836.SH</t>
+          <t>245964.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>37.49</v>
+      </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26新乡投资PPN002</t>
+          <t>25苏农02</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>2.24Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.8637</t>
+          <t>1.6973</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -9760,12 +9788,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>新乡投资集团有限公司</t>
+          <t>苏州市农业发展集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C 29.74</t>
+          <t>D- 2.56</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9785,17 +9813,21 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U43" s="3"/>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X43" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -9804,17 +9836,17 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>河南省-新乡市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还即将到期公司债券本金。[23 新乡03]</t>
+          <t>本期债券募集资金7.00亿元扣除发行费用后,4.00亿元用于偿还到期公司债券本金,剩余全部用于偿还其他有息负债。[21苏农02]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国联民生证券承销保荐有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD43" s="3"/>
@@ -9835,17 +9867,17 @@
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>新乡投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
+          <t>苏州市农业发展集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
@@ -9856,22 +9888,22 @@
       </c>
       <c r="AM43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AN43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ43" s="3" t="inlineStr">
@@ -9881,17 +9913,17 @@
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -9906,12 +9938,12 @@
       </c>
       <c r="AW43" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX43" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY43" s="3" t="inlineStr">
@@ -9924,7 +9956,7 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26临开Y1</t>
+          <t>26上金02</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -9934,58 +9966,62 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>283847.SH</t>
+          <t>245969.SH</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>29.85</v>
+      </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>25临开Y1</t>
+          <t>26上金01</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>1.65Y+N</t>
+          <t>2.60Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>1.8122</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>杭州临平开发投资集团有限公司</t>
+          <t>上海汽车集团金控管理有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>C- 11.54</t>
+          <t>B- 38.45</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10005,36 +10041,40 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X44" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还公司债券本金。[23临开Y1]</t>
+          <t>本期公司债券募集资金拟用于偿还到期公司债券[23上金K2]</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD44" s="3"/>
@@ -10055,20 +10095,24 @@
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>杭州临平开发投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
+          <t>上海汽车集团金控管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
-        </is>
-      </c>
-      <c r="AK44" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK44" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL44" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10081,37 +10125,37 @@
       </c>
       <c r="AN44" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP44" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ44" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT44" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU44" s="3" t="inlineStr">
@@ -10126,7 +10170,7 @@
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10144,55 +10188,57 @@
     <row r="45" customHeight="true" ht="18.0">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>26中远海运MTN007(科创债)</t>
+          <t>26舟交02</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>102683436.IB</t>
+          <t>245968.SH</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>15Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>50.0</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>50.0</v>
-      </c>
+        <v>6.0</v>
+      </c>
+      <c r="F45" s="3"/>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>43.85</v>
+      </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>24中远海运MTN001</t>
+          <t>26舟山交投MTN002</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>12.96Y</t>
+          <t>4.75Y</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2.1444</t>
+          <t>1.8479</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -10202,12 +10248,12 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>中国远洋海运集团有限公司</t>
+          <t>舟山交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C 26.93</t>
+          <t>C- 16.98</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10217,7 +10263,7 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
@@ -10227,61 +10273,61 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>2.13%~2.23%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z45" s="3"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>浙江省-舟山市</t>
         </is>
       </c>
       <c r="AB45" s="3" t="inlineStr">
         <is>
-          <t>发行人拟将本次募集资金50亿元用于偿还发行人本部及合并报表范围内子公司的有息债务及支付船舶建造款</t>
+          <t>本期公司债券募集资金扣除发行费用后,发行人拟将6亿元用于偿还到期的公司债券本金[21舟交02]</t>
         </is>
       </c>
       <c r="AC45" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司,中国银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD45" s="3"/>
       <c r="AE45" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF45" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG45" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH45" s="3" t="inlineStr">
         <is>
-          <t>中国远洋海运集团有限公司2026年度第七期科技创新债券</t>
+          <t>舟山交通投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI45" s="3" t="inlineStr">
@@ -10291,48 +10337,52 @@
       </c>
       <c r="AJ45" s="3" t="inlineStr">
         <is>
-          <t>2041-08-28</t>
-        </is>
-      </c>
-      <c r="AK45" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK45" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL45" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AM45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP45" s="3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ45" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT45" s="3" t="inlineStr">
@@ -10370,72 +10420,70 @@
     <row r="46" customHeight="true" ht="18.0">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>26新凤鸣控SCP005</t>
+          <t>26医产K1</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>012682168.IB</t>
+          <t>520443.SZ</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>3.0</v>
+      </c>
+      <c r="F46" s="3"/>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>1.45 ~ 1.65</t>
-        </is>
-      </c>
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
+          <t>1.60 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>58.49</v>
+      </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>26新凤鸣控SCP004</t>
+          <t>26君实生物MTN003(科创债)</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>180D</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>1.6342</t>
+          <t>2.7236</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.7100</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>新凤鸣控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.33</t>
-        </is>
-      </c>
+          <t>四川生物医药产业集团有限责任公司</t>
+        </is>
+      </c>
+      <c r="P46" s="3"/>
       <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -10443,7 +10491,7 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -10453,21 +10501,17 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t>1.65%~1.69%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X46" s="3"/>
       <c r="Y46" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -10476,64 +10520,64 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
-          <t>浙江省-嘉兴市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB46" s="3" t="inlineStr">
         <is>
-          <t>本期发行超短期融资券2亿元,用于偿还发行人到期的债务融资工具本金。[25新凤鸣控SCP004]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不低于2.10亿元用于股权投资;不低于0.71亿元用于认购基金份额;剩余部分用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC46" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,北京银行股份有限公司</t>
+          <t>中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD46" s="3"/>
       <c r="AE46" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF46" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG46" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH46" s="3" t="inlineStr">
         <is>
-          <t>新凤鸣控股集团有限公司2026年度第五期超短期融资券</t>
+          <t>四川生物医药产业集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)(用于生物医药)</t>
         </is>
       </c>
       <c r="AI46" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ46" s="3" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM46" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN46" s="3" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AM46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO46" s="3" t="inlineStr">
@@ -10544,22 +10588,22 @@
       <c r="AP46" s="3"/>
       <c r="AQ46" s="3" t="inlineStr">
         <is>
-          <t>化工制造</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR46" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AS46" s="3" t="inlineStr">
         <is>
-          <t>化学制品</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AT46" s="3" t="inlineStr">
         <is>
-          <t>化学纤维</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU46" s="3" t="inlineStr">
@@ -10592,7 +10636,7 @@
     <row r="47" customHeight="true" ht="18.0">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>26苏农01</t>
+          <t>26金城02</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -10602,7 +10646,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>245964.SH</t>
+          <t>283812.SH</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
@@ -10611,7 +10655,7 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>7.0</v>
+        <v>5.0</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="inlineStr">
@@ -10619,26 +10663,30 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
+      <c r="H47" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>50.49</v>
+      </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>25苏农02</t>
+          <t>26金城01</t>
         </is>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2.24Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>1.6908</t>
+          <t>1.7269</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -10648,12 +10696,12 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>苏州市农业发展集团有限公司</t>
+          <t>张家港市金城投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>D- 2.56</t>
+          <t>C- 24.77</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -10673,24 +10721,24 @@
       </c>
       <c r="T47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X47" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z47" s="3"/>
@@ -10701,12 +10749,12 @@
       </c>
       <c r="AB47" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金7.00亿元扣除发行费用后,4.00亿元用于偿还到期公司债券本金,剩余全部用于偿还其他有息负债。[21苏农02]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[23 金城04]</t>
         </is>
       </c>
       <c r="AC47" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>东吴证券股份有限公司,国金证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD47" s="3"/>
@@ -10727,17 +10775,17 @@
       </c>
       <c r="AH47" s="3" t="inlineStr">
         <is>
-          <t>苏州市农业发展集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>张家港市金城投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI47" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ47" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK47" s="3"/>
@@ -10748,17 +10796,17 @@
       </c>
       <c r="AM47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AN47" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO47" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP47" s="3" t="inlineStr">
@@ -10773,17 +10821,17 @@
       </c>
       <c r="AR47" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS47" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT47" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU47" s="3" t="inlineStr">
@@ -10816,7 +10864,7 @@
     <row r="48" customHeight="true" ht="18.0">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>26上金02</t>
+          <t>26济运01</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -10826,7 +10874,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>245969.SH</t>
+          <t>283795.SH</t>
         </is>
       </c>
       <c r="D48" s="3" t="inlineStr">
@@ -10835,49 +10883,53 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>16.0</v>
+        <v>0.23</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+          <t>2.00 ~ 3.20</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>133.85</v>
+      </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>26上金01</t>
+          <t>24济运04</t>
         </is>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2.60Y</t>
+          <t>2.97Y</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>1.6732</t>
+          <t>2.0553</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
         <is>
-          <t>1.7300/1.6900</t>
+          <t>2.0600/--</t>
         </is>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>上海汽车集团金控管理有限公司</t>
+          <t>济宁市城运集团有限公司</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
         <is>
-          <t>B- 42.20</t>
+          <t>B- 37.50</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
@@ -10897,40 +10949,40 @@
       </c>
       <c r="T48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z48" s="3"/>
       <c r="AA48" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>山东省-济宁市</t>
         </is>
       </c>
       <c r="AB48" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟用于偿还到期公司债券[23上金K2]</t>
+          <t>本期债券募集资金0.23亿元,扣除发行费用后拟用于偿还公司债券本金或置换偿还到期公司债券本金的自有资金[23任兴03,23任兴04,23任城04]</t>
         </is>
       </c>
       <c r="AC48" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,平安证券股份有限公司</t>
+          <t>国投证券股份有限公司,恒泰长财证券有限责任公司,长城证券股份有限公司,申港证券股份有限公司</t>
         </is>
       </c>
       <c r="AD48" s="3"/>
@@ -10951,24 +11003,20 @@
       </c>
       <c r="AH48" s="3" t="inlineStr">
         <is>
-          <t>上海汽车集团金控管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>济宁市城运集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI48" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ48" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK48" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="AK48" s="3"/>
       <c r="AL48" s="3" t="inlineStr">
         <is>
           <t/>
@@ -10981,37 +11029,37 @@
       </c>
       <c r="AN48" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO48" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP48" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ48" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR48" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS48" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT48" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU48" s="3" t="inlineStr">
@@ -11044,70 +11092,68 @@
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26绿金租赁MTN001</t>
+          <t>26蚌水02</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>102683413.IB</t>
+          <t>283758.SH</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>2.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F49" s="3"/>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.40</t>
+          <t>1.90 ~ 2.90</t>
         </is>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="K49" s="3" t="inlineStr">
         <is>
-          <t>25绿金租赁GZ01</t>
+          <t>25邕振V1</t>
         </is>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>1.98Y</t>
+          <t>3.67Y+5.00Y</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>2.3658</t>
+          <t>2.0953</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
         <is>
-          <t>--/2.0000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>广东绿金融资租赁有限公司</t>
+          <t>蚌埠靓淮河水利投资集团有限公司</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11117,7 +11163,7 @@
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -11134,12 +11180,12 @@
       <c r="V49" s="3"/>
       <c r="W49" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>2.38%~2.48%</t>
+          <t>2.20%~2.30%</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr">
@@ -11147,26 +11193,34 @@
           <t>AA</t>
         </is>
       </c>
-      <c r="Z49" s="3"/>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>AA+</t>
+        </is>
+      </c>
       <c r="AA49" s="3" t="inlineStr">
         <is>
-          <t>广东省-佛山市</t>
+          <t>安徽省-蚌埠市</t>
         </is>
       </c>
       <c r="AB49" s="3" t="inlineStr">
         <is>
-          <t>发行人本次发行2亿元中期票据,募集资金拟用于偿还发行人的金融机构借款</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将5亿元用于偿还到期公司债本金[23蚌水01]</t>
         </is>
       </c>
       <c r="AC49" s="3" t="inlineStr">
         <is>
-          <t>广东顺德农村商业银行股份有限公司,广东南海农村商业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD49" s="3"/>
+          <t>招商证券股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr">
+        <is>
+          <t>蚌埠市国有资本运营控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE49" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF49" s="3" t="inlineStr">
@@ -11176,33 +11230,33 @@
       </c>
       <c r="AG49" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>广东绿金融资租赁有限公司2026年度第一期中期票据</t>
+          <t>蚌埠靓淮河水利投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ49" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AM49" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AN49" s="3" t="inlineStr">
@@ -11212,32 +11266,32 @@
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP49" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ49" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR49" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS49" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT49" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU49" s="3" t="inlineStr">
@@ -11247,7 +11301,7 @@
       </c>
       <c r="AV49" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW49" s="3" t="inlineStr">
@@ -11270,70 +11324,68 @@
     <row r="50" customHeight="true" ht="18.0">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>26淮安交通MTN003</t>
+          <t>26蚌水01</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>102683421.IB</t>
+          <t>283752.SH</t>
         </is>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>4.6</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F50" s="3"/>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.40</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>26淮安交通MTN002</t>
+          <t>25邕振V1</t>
         </is>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>1.80Y</t>
+          <t>3.67Y+5.00Y</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>1.6752</t>
+          <t>2.0953</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>淮安市交通控股集团有限公司</t>
+          <t>蚌埠靓淮河水利投资集团有限公司</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>C- 19.16</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11343,7 +11395,7 @@
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -11360,39 +11412,47 @@
       <c r="V50" s="3"/>
       <c r="W50" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.08%~2.18%</t>
         </is>
       </c>
       <c r="Y50" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z50" s="3" t="inlineStr">
+        <is>
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z50" s="3"/>
       <c r="AA50" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>安徽省-蚌埠市</t>
         </is>
       </c>
       <c r="AB50" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额4.6亿元,根据发行人的资金需求,拟全部用于偿还发行人债务融资工具本金[26淮安交通CP002]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将5亿元用于偿还到期公司债本金[23蚌水01]</t>
         </is>
       </c>
       <c r="AC50" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,杭州银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD50" s="3"/>
+          <t>招商证券股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD50" s="3" t="inlineStr">
+        <is>
+          <t>蚌埠市国有资本运营控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE50" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF50" s="3" t="inlineStr">
@@ -11402,28 +11462,28 @@
       </c>
       <c r="AG50" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH50" s="3" t="inlineStr">
         <is>
-          <t>淮安市交通控股集团有限公司2026年度第三期中期票据</t>
+          <t>蚌埠靓淮河水利投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI50" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ50" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK50" s="3"/>
       <c r="AL50" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AM50" s="3" t="inlineStr">
@@ -11438,12 +11498,12 @@
       </c>
       <c r="AO50" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP50" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ50" s="3" t="inlineStr">
@@ -11453,12 +11513,12 @@
       </c>
       <c r="AR50" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS50" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT50" s="3" t="inlineStr">
@@ -11473,7 +11533,7 @@
       </c>
       <c r="AV50" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW50" s="3" t="inlineStr">
@@ -11496,70 +11556,72 @@
     <row r="51" customHeight="true" ht="18.0">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>26渝保税MTN002</t>
+          <t>26京城01</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>102683415.IB</t>
+          <t>283799.SH</t>
         </is>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="F51" s="4" t="n">
-        <v>12.0</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="F51" s="3"/>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>106.49</v>
+      </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
-          <t>26渝保税MTN001</t>
+          <t>25京城01</t>
         </is>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>4.58Y</t>
+          <t>1.79Y</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1.8396</t>
+          <t>1.9331</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
         <is>
-          <t>1.8650/1.8400</t>
+          <t>--/1.8800</t>
         </is>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>重庆保税港区开发管理集团有限公司</t>
+          <t>北京城建投资发展股份有限公司</t>
         </is>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C 30.00</t>
+          <t>B 52.11</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -11569,7 +11631,7 @@
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>08-27 14:00</t>
+          <t>08-27 16:00</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr">
@@ -11579,46 +11641,42 @@
       </c>
       <c r="T51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
       <c r="W51" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X51" s="3" t="inlineStr">
-        <is>
-          <t>1.84%~1.94%</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X51" s="3"/>
       <c r="Y51" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z51" s="3"/>
       <c r="AA51" s="3" t="inlineStr">
         <is>
-          <t>重庆市-两江新区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB51" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额12亿元,全部用于偿还发行人本部债务融资工具本金[25渝保税SCP002]</t>
+          <t>本期债券募集资金4亿元拟全部用于偿还公司债券本金[24北城01]</t>
         </is>
       </c>
       <c r="AC51" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,重庆农村商业银行股份有限公司</t>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
         </is>
       </c>
       <c r="AD51" s="3"/>
       <c r="AE51" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF51" s="3" t="inlineStr">
@@ -11628,28 +11686,32 @@
       </c>
       <c r="AG51" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH51" s="3" t="inlineStr">
         <is>
-          <t>重庆保税港区开发管理集团有限公司2026年度第二期中期票据</t>
+          <t>北京城建投资发展股份有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI51" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ51" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
-        </is>
-      </c>
-      <c r="AK51" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK51" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AM51" s="3" t="inlineStr">
@@ -11659,37 +11721,37 @@
       </c>
       <c r="AN51" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP51" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ51" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>综合地产开发</t>
         </is>
       </c>
       <c r="AT51" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU51" s="3" t="inlineStr">
@@ -11722,17 +11784,17 @@
     <row r="52" customHeight="true" ht="18.0">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>26海南农垦MTN001(并购)</t>
+          <t>26泗洪01</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>102683430.IB</t>
+          <t>283814.SH</t>
         </is>
       </c>
       <c r="D52" s="3" t="inlineStr">
@@ -11741,36 +11803,30 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="F52" s="4" t="n">
-        <v>8.0</v>
-      </c>
+        <v>10.0</v>
+      </c>
+      <c r="F52" s="3"/>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 1.90</t>
-        </is>
-      </c>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>55.85</v>
+      </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="K52" s="3" t="inlineStr">
-        <is>
-          <t>23海南农垦MTN002(乡村振兴)</t>
-        </is>
-      </c>
-      <c r="L52" s="3" t="inlineStr">
-        <is>
-          <t>2.25Y+5.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1.7077</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -11780,12 +11836,12 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>海南省农垦投资控股集团有限公司</t>
+          <t>泗洪县宏源公有资产经营集团有限公司</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>C+ 31.16</t>
+          <t>D 4.76</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -11795,7 +11851,7 @@
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>08-27 10:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -11812,39 +11868,39 @@
       <c r="V52" s="3"/>
       <c r="W52" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z52" s="3"/>
       <c r="AA52" s="3" t="inlineStr">
         <is>
-          <t>海南省-海口市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB52" s="3" t="inlineStr">
         <is>
-          <t>本期拟发行8亿元人民币，其中4.2亿元用于支付本次重组的增资扩股第一期款项，3.8亿元用于补充本部或子公司流动资金。</t>
+          <t>本期公司债券发行总额不超过人民币10亿元(含10亿元),发行人在扣除发行费用后,全部用于偿还回售的公司债券本金[23泗洪01]</t>
         </is>
       </c>
       <c r="AC52" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
+          <t>中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD52" s="3"/>
       <c r="AE52" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF52" s="3" t="inlineStr">
@@ -11854,17 +11910,17 @@
       </c>
       <c r="AG52" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH52" s="3" t="inlineStr">
         <is>
-          <t>海南省农垦投资控股集团有限公司2026年度第一期中期票据(并购)</t>
+          <t>泗洪县宏源公有资产经营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI52" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ52" s="3" t="inlineStr">
@@ -11875,7 +11931,7 @@
       <c r="AK52" s="3"/>
       <c r="AL52" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AM52" s="3" t="inlineStr">
@@ -11895,27 +11951,27 @@
       </c>
       <c r="AP52" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ52" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR52" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS52" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT52" s="3" t="inlineStr">
         <is>
-          <t>种植业</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU52" s="3" t="inlineStr">
@@ -11943,62 +11999,62 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ52" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ52" s="3"/>
     </row>
     <row r="53" customHeight="true" ht="18.0">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>26常德经建MTN003</t>
+          <t>26国新01</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>102683427.IB</t>
+          <t>245985.SH</t>
         </is>
       </c>
       <c r="D53" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F53" s="4" t="n">
-        <v>4.3</v>
-      </c>
+        <v>20.0</v>
+      </c>
+      <c r="F53" s="3"/>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>30.85</v>
+      </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>24常德经建MTN003</t>
+          <t>21国新控股MTN002</t>
         </is>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>3.06Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1.7807</t>
+          <t>1.7413</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -12008,12 +12064,12 @@
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>常德市经济建设投资集团有限公司</t>
+          <t>中国国新控股有限责任公司</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>B- 44.91</t>
+          <t>A- 66.58</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12023,7 +12079,7 @@
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -12040,54 +12096,54 @@
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.69%~1.79%</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z53" s="3"/>
       <c r="AA53" s="3" t="inlineStr">
         <is>
-          <t>湖南省-常德市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB53" s="3" t="inlineStr">
         <is>
-          <t>发行人本次中期票据注册额度50亿元,本期发行规模为4.3亿元,募集资金拟全部用于偿还发行人本部存量有息债务。[23常德经建MTN003]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于生产性支出,包括但不限于补充流动资金、偿还有息债务等符合法律法规及监管要求的用途</t>
         </is>
       </c>
       <c r="AC53" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,华夏银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,国新证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD53" s="3"/>
       <c r="AE53" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF53" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG53" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH53" s="3" t="inlineStr">
         <is>
-          <t>常德市经济建设投资集团有限公司2026年度第三期中期票据</t>
+          <t>中国国新控股有限责任公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI53" s="3" t="inlineStr">
@@ -12103,7 +12159,7 @@
       <c r="AK53" s="3"/>
       <c r="AL53" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AM53" s="3" t="inlineStr">
@@ -12123,32 +12179,32 @@
       </c>
       <c r="AP53" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ53" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR53" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS53" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT53" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU53" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV53" s="3" t="inlineStr">
@@ -12158,7 +12214,7 @@
       </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX53" s="3" t="inlineStr">
@@ -12176,7 +12232,7 @@
     <row r="54" customHeight="true" ht="18.0">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>26中冶MTN002</t>
+          <t>26绿金租赁MTN001</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -12186,60 +12242,60 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>102683422.IB</t>
+          <t>102683413.IB</t>
         </is>
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>20.0</v>
+        <v>2.0</v>
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.10</t>
+          <t>1.90 ~ 2.40</t>
         </is>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>24中冶MTN010</t>
+          <t>25绿金租赁GZ01</t>
         </is>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>3.00Y+N</t>
+          <t>1.98Y</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1.7599</t>
+          <t>2.2996</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
         <is>
-          <t>1.7700/1.7500</t>
+          <t>--/2.0000</t>
         </is>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>中国冶金科工股份有限公司</t>
+          <t>广东绿金融资租赁有限公司</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>C 29.69</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12266,37 +12322,33 @@
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.38%~2.48%</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z54" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z54" s="3"/>
       <c r="AA54" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>广东省-佛山市</t>
         </is>
       </c>
       <c r="AB54" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为人民币20亿元。所募资金将用于偿还公司本部及子公司到期债务、补充营运资金</t>
+          <t>发行人本次发行2亿元中期票据,募集资金拟用于偿还发行人的金融机构借款</t>
         </is>
       </c>
       <c r="AC54" s="3" t="inlineStr">
         <is>
-          <t>中国邮政储蓄银行股份有限公司,北京银行股份有限公司,华夏银行股份有限公司</t>
+          <t>广东顺德农村商业银行股份有限公司,广东南海农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD54" s="3"/>
@@ -12307,7 +12359,7 @@
       </c>
       <c r="AF54" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG54" s="3" t="inlineStr">
@@ -12317,7 +12369,7 @@
       </c>
       <c r="AH54" s="3" t="inlineStr">
         <is>
-          <t>中国冶金科工股份有限公司2026年度第二期中期票据</t>
+          <t>广东绿金融资租赁有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI54" s="3" t="inlineStr">
@@ -12338,7 +12390,7 @@
       </c>
       <c r="AM54" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AN54" s="3" t="inlineStr">
@@ -12348,32 +12400,32 @@
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP54" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ54" s="3" t="inlineStr">
         <is>
-          <t>建筑施工</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
         <is>
-          <t>综合建筑施工</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT54" s="3" t="inlineStr">
         <is>
-          <t>专业工程</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU54" s="3" t="inlineStr">
@@ -12388,12 +12440,12 @@
       </c>
       <c r="AW54" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX54" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY54" s="3" t="inlineStr">
@@ -12401,14 +12453,12 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ54" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ54" s="3"/>
     </row>
     <row r="55" customHeight="true" ht="18.0">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>26柳州东投MTN001A</t>
+          <t>26淮安交通MTN003</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -12418,60 +12468,60 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>102683439.IB</t>
+          <t>102683421.IB</t>
         </is>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
-          <t>2+2+1</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1.5</v>
+        <v>4.6</v>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>1.70 ~ 2.40</t>
         </is>
       </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>25柳州东投MTN002</t>
+          <t>26淮安交通MTN002</t>
         </is>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2.00Y+2.00Y</t>
+          <t>1.80Y</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1.9959</t>
+          <t>1.6752</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>广西柳州市东城投资开发集团有限公司</t>
+          <t>淮安市交通控股集团有限公司</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
-          <t>C- 13.45</t>
+          <t>C- 17.97</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
@@ -12481,7 +12531,7 @@
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>08-27 14:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -12498,12 +12548,12 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y55" s="3" t="inlineStr">
@@ -12514,17 +12564,17 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-柳州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB55" s="3" t="inlineStr">
         <is>
-          <t>公司发行本期中期票据规模不超过3亿元,用于优化债务结构,所偿还债务均不属于政府隐性债务。[23柳州东投MTN001]</t>
+          <t>本期中期票据发行金额4.6亿元,根据发行人的资金需求,拟全部用于偿还发行人债务融资工具本金[26淮安交通CP002]</t>
         </is>
       </c>
       <c r="AC55" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,广西北部湾银行股份有限公司</t>
+          <t>中信银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD55" s="3"/>
@@ -12545,7 +12595,7 @@
       </c>
       <c r="AH55" s="3" t="inlineStr">
         <is>
-          <t>广西柳州市东城投资开发集团有限公司2026年度第一期中期票据(品种一)</t>
+          <t>淮安市交通控股集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI55" s="3" t="inlineStr">
@@ -12581,7 +12631,7 @@
       </c>
       <c r="AP55" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ55" s="3" t="inlineStr">
@@ -12591,12 +12641,12 @@
       </c>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT55" s="3" t="inlineStr">
@@ -12606,7 +12656,7 @@
       </c>
       <c r="AU55" s="3" t="inlineStr">
         <is>
-          <t>2028-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV55" s="3" t="inlineStr">
@@ -12616,7 +12666,7 @@
       </c>
       <c r="AW55" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX55" s="3" t="inlineStr">
@@ -12634,7 +12684,7 @@
     <row r="56" customHeight="true" ht="18.0">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>26粤铁建MTN004</t>
+          <t>26渝保税MTN002</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
@@ -12644,60 +12694,60 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>102683437.IB</t>
+          <t>102683415.IB</t>
         </is>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 1.90</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>26粤铁建MTN003</t>
+          <t>26渝保税MTN001</t>
         </is>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>1.82Y</t>
+          <t>4.58Y</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>1.6157</t>
+          <t>1.8396</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
-          <t>1.6300/1.6100</t>
+          <t>1.8650/1.8400</t>
         </is>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>广东省铁路建设投资集团有限公司</t>
+          <t>重庆保税港区开发管理集团有限公司</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>B 53.33</t>
+          <t>C 28.44</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -12707,7 +12757,7 @@
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 14:00</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -12724,33 +12774,33 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>1.64%~1.74%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3" t="inlineStr">
         <is>
-          <t>广东省</t>
+          <t>重庆市-两江新区</t>
         </is>
       </c>
       <c r="AB56" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额10亿元,拟偿还发行人有息负债</t>
+          <t>发行人本期中期票据发行金额12亿元,全部用于偿还发行人本部债务融资工具本金[25渝保税SCP002]</t>
         </is>
       </c>
       <c r="AC56" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,重庆农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD56" s="3"/>
@@ -12771,7 +12821,7 @@
       </c>
       <c r="AH56" s="3" t="inlineStr">
         <is>
-          <t>广东省铁路建设投资集团有限公司2026年度第四期中期票据</t>
+          <t>重庆保税港区开发管理集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI56" s="3" t="inlineStr">
@@ -12781,7 +12831,7 @@
       </c>
       <c r="AJ56" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK56" s="3"/>
@@ -12802,12 +12852,12 @@
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP56" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ56" s="3" t="inlineStr">
@@ -12817,17 +12867,17 @@
       </c>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
         <is>
-          <t>轨道交通</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT56" s="3" t="inlineStr">
         <is>
-          <t>铁路运输</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU56" s="3" t="inlineStr">
@@ -12860,7 +12910,7 @@
     <row r="57" customHeight="true" ht="18.0">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>26华光环保SCP017</t>
+          <t>26海南农垦MTN001(并购)</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
@@ -12870,60 +12920,60 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>012682170.IB</t>
+          <t>102683430.IB</t>
         </is>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>0.59Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.00</t>
+          <t>1.60 ~ 1.90</t>
         </is>
       </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>26华光环保SCP016</t>
+          <t>23海南农垦MTN002(乡村振兴)</t>
         </is>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>218D</t>
+          <t>2.25Y+5.00Y</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>1.5223</t>
+          <t>1.7077</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
-          <t>1.5400/1.4800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>无锡华光环保能源集团股份有限公司</t>
+          <t>海南省农垦投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C- 12.79</t>
+          <t>C+ 31.16</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -12933,7 +12983,7 @@
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 10:00</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -12950,12 +13000,12 @@
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X57" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
@@ -12966,23 +13016,23 @@
       <c r="Z57" s="3"/>
       <c r="AA57" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>海南省-海口市</t>
         </is>
       </c>
       <c r="AB57" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟发行1.00亿元，用于偿还发行人有息负债[26华光环保SCP006（科创债）]</t>
+          <t>本期拟发行8亿元人民币，其中4.2亿元用于支付本次重组的增资扩股第一期款项，3.8亿元用于补充本部或子公司流动资金。</t>
         </is>
       </c>
       <c r="AC57" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,中国民生银行股份有限公司</t>
+          <t>兴业银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD57" s="3"/>
       <c r="AE57" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF57" s="3" t="inlineStr">
@@ -12997,7 +13047,7 @@
       </c>
       <c r="AH57" s="3" t="inlineStr">
         <is>
-          <t>无锡华光环保能源集团股份有限公司2026年度第十七期超短期融资券</t>
+          <t>海南省农垦投资控股集团有限公司2026年度第一期中期票据(并购)</t>
         </is>
       </c>
       <c r="AI57" s="3" t="inlineStr">
@@ -13007,7 +13057,7 @@
       </c>
       <c r="AJ57" s="3" t="inlineStr">
         <is>
-          <t>2027-04-02</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK57" s="3"/>
@@ -13033,32 +13083,32 @@
       </c>
       <c r="AP57" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ57" s="3" t="inlineStr">
         <is>
-          <t>电力设备制造</t>
+          <t>农林牧渔</t>
         </is>
       </c>
       <c r="AR57" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AS57" s="3" t="inlineStr">
         <is>
-          <t>其他电力设备</t>
+          <t>综合农林牧渔</t>
         </is>
       </c>
       <c r="AT57" s="3" t="inlineStr">
         <is>
-          <t>专用设备</t>
+          <t>种植业</t>
         </is>
       </c>
       <c r="AU57" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AV57" s="3" t="inlineStr">
@@ -13068,7 +13118,7 @@
       </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX57" s="3" t="inlineStr">
@@ -13081,12 +13131,14 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ57" s="3"/>
+      <c r="AZ57" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>26温州国投SCP002</t>
+          <t>26常德经建MTN003</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -13096,60 +13148,60 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>012682166.IB</t>
+          <t>102683427.IB</t>
         </is>
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>5.0</v>
+        <v>4.3</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>5.0</v>
+        <v>4.3</v>
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 1.80</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>26温州国投SCP001</t>
+          <t>24常德经建MTN003</t>
         </is>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>149D</t>
+          <t>3.06Y</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>1.5326</t>
+          <t>1.7807</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
         <is>
-          <t>1.5900/1.5200</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>温州市国有资本投资运营有限公司</t>
+          <t>常德市经济建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.93</t>
+          <t>B- 44.17</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
@@ -13176,39 +13228,39 @@
       <c r="V58" s="3"/>
       <c r="W58" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.58%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y58" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z58" s="3"/>
       <c r="AA58" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>湖南省-常德市</t>
         </is>
       </c>
       <c r="AB58" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券拟发行金额为5亿元人民币,期限为270天,所募集资金用于偿还发行人及其下属子公司的银行流贷。</t>
+          <t>发行人本次中期票据注册额度50亿元,本期发行规模为4.3亿元,募集资金拟全部用于偿还发行人本部存量有息债务。[23常德经建MTN003]</t>
         </is>
       </c>
       <c r="AC58" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,中国光大银行股份有限公司</t>
+          <t>兴业银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD58" s="3"/>
       <c r="AE58" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF58" s="3" t="inlineStr">
@@ -13223,7 +13275,7 @@
       </c>
       <c r="AH58" s="3" t="inlineStr">
         <is>
-          <t>温州市国有资本投资运营有限公司2026年度第二期超短期融资券</t>
+          <t>常德市经济建设投资集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI58" s="3" t="inlineStr">
@@ -13233,7 +13285,7 @@
       </c>
       <c r="AJ58" s="3" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK58" s="3"/>
@@ -13259,32 +13311,32 @@
       </c>
       <c r="AP58" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ58" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT58" s="3" t="inlineStr">
         <is>
-          <t>饮料制造</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU58" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AV58" s="3" t="inlineStr">
@@ -13294,7 +13346,7 @@
       </c>
       <c r="AW58" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX58" s="3" t="inlineStr">
@@ -13312,7 +13364,7 @@
     <row r="59" customHeight="true" ht="18.0">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>26桂国控SCP006</t>
+          <t>26中冶MTN002</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -13322,60 +13374,60 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>012682169.IB</t>
+          <t>102683422.IB</t>
         </is>
       </c>
       <c r="D59" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>7.0</v>
+        <v>20.0</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>7.0</v>
+        <v>20.0</v>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>1.39 ~ 1.69</t>
+          <t>1.50 ~ 2.10</t>
         </is>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>26桂国控SCP004</t>
+          <t>24中冶MTN010</t>
         </is>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>268D</t>
+          <t>3.00Y+N</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>1.6094</t>
+          <t>1.7599</t>
         </is>
       </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7500</t>
         </is>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>广西国控资本运营集团有限责任公司</t>
+          <t>中国冶金科工股份有限公司</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 14.63</t>
+          <t>C 29.78</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13402,12 +13454,12 @@
       <c r="V59" s="3"/>
       <c r="W59" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>1.53%~1.57%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -13415,31 +13467,35 @@
           <t>AAA</t>
         </is>
       </c>
-      <c r="Z59" s="3"/>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA59" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB59" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金全部用于归还发行人本部及下属公司的有息债务。</t>
+          <t>本期债务融资工具发行规模为人民币20亿元。所募资金将用于偿还公司本部及子公司到期债务、补充营运资金</t>
         </is>
       </c>
       <c r="AC59" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,渤海银行股份有限公司</t>
+          <t>中国邮政储蓄银行股份有限公司,北京银行股份有限公司,华夏银行股份有限公司</t>
         </is>
       </c>
       <c r="AD59" s="3"/>
       <c r="AE59" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF59" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG59" s="3" t="inlineStr">
@@ -13449,7 +13505,7 @@
       </c>
       <c r="AH59" s="3" t="inlineStr">
         <is>
-          <t>广西国控资本运营集团有限责任公司2026年度第六期超短期融资券</t>
+          <t>中国冶金科工股份有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI59" s="3" t="inlineStr">
@@ -13459,7 +13515,7 @@
       </c>
       <c r="AJ59" s="3" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK59" s="3"/>
@@ -13485,27 +13541,27 @@
       </c>
       <c r="AP59" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ59" s="3" t="inlineStr">
         <is>
-          <t>农林牧渔</t>
+          <t>建筑施工</t>
         </is>
       </c>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
         <is>
-          <t>综合农林牧渔</t>
+          <t>综合建筑施工</t>
         </is>
       </c>
       <c r="AT59" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>专业工程</t>
         </is>
       </c>
       <c r="AU59" s="3" t="inlineStr">
@@ -13520,12 +13576,12 @@
       </c>
       <c r="AW59" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX59" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY59" s="3" t="inlineStr">
@@ -13534,13 +13590,13 @@
         </is>
       </c>
       <c r="AZ59" s="4" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>26蚌水02</t>
+          <t>26柳州东投MTN001A</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -13550,43 +13606,45 @@
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>283758.SH</t>
+          <t>102683439.IB</t>
         </is>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>2+2+1</t>
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F60" s="3"/>
+        <v>1.5</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>25邕振V1</t>
+          <t>25柳州东投MTN002</t>
         </is>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>3.67Y+5.00Y</t>
+          <t>2.00Y+2.00Y</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>2.0916</t>
+          <t>1.9959</t>
         </is>
       </c>
       <c r="N60" s="3" t="inlineStr">
@@ -13596,12 +13654,12 @@
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>蚌埠靓淮河水利投资集团有限公司</t>
+          <t>广西柳州市东城投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 13.45</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -13611,7 +13669,7 @@
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 14:00</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr">
@@ -13628,47 +13686,39 @@
       <c r="V60" s="3"/>
       <c r="W60" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X60" s="3" t="inlineStr">
         <is>
-          <t>2.20%~2.30%</t>
+          <t>2.00%~2.10%</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z60" s="3" t="inlineStr">
-        <is>
           <t>AA+</t>
         </is>
       </c>
+      <c r="Z60" s="3"/>
       <c r="AA60" s="3" t="inlineStr">
         <is>
-          <t>安徽省-蚌埠市</t>
+          <t>广西壮族自治区-柳州市</t>
         </is>
       </c>
       <c r="AB60" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将5亿元用于偿还到期公司债本金[23蚌水01]</t>
+          <t>公司发行本期中期票据规模不超过3亿元,用于优化债务结构,所偿还债务均不属于政府隐性债务。[23柳州东投MTN001]</t>
         </is>
       </c>
       <c r="AC60" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD60" s="3" t="inlineStr">
-        <is>
-          <t>蚌埠市国有资本运营控股集团有限公司</t>
-        </is>
-      </c>
+          <t>东方证券股份有限公司,广西北部湾银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD60" s="3"/>
       <c r="AE60" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF60" s="3" t="inlineStr">
@@ -13678,17 +13728,17 @@
       </c>
       <c r="AG60" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH60" s="3" t="inlineStr">
         <is>
-          <t>蚌埠靓淮河水利投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>广西柳州市东城投资开发集团有限公司2026年度第一期中期票据(品种一)</t>
         </is>
       </c>
       <c r="AI60" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ60" s="3" t="inlineStr">
@@ -13699,7 +13749,7 @@
       <c r="AK60" s="3"/>
       <c r="AL60" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM60" s="3" t="inlineStr">
@@ -13714,7 +13764,7 @@
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP60" s="3" t="inlineStr">
@@ -13729,12 +13779,12 @@
       </c>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT60" s="3" t="inlineStr">
@@ -13744,17 +13794,17 @@
       </c>
       <c r="AU60" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2028-08-28</t>
         </is>
       </c>
       <c r="AV60" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW60" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX60" s="3" t="inlineStr">
@@ -13772,7 +13822,7 @@
     <row r="61" customHeight="true" ht="18.0">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>26闽国资MTN001</t>
+          <t>26粤铁建MTN004</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
@@ -13782,7 +13832,7 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>102683420.IB</t>
+          <t>102683437.IB</t>
         </is>
       </c>
       <c r="D61" s="3" t="inlineStr">
@@ -13791,51 +13841,51 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>4.0</v>
+        <v>10.0</v>
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.10</t>
+          <t>1.40 ~ 1.90</t>
         </is>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>25闽国资MTN002(科创债)</t>
+          <t>26粤铁建MTN003</t>
         </is>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>2.06Y</t>
+          <t>1.82Y</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>1.6898</t>
+          <t>1.6157</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6100</t>
         </is>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>福建省国有资产管理有限公司</t>
+          <t>广东省铁路建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C- 20.67</t>
+          <t>B 53.33</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -13862,33 +13912,33 @@
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
-          <t>1.66%~1.76%</t>
+          <t>1.64%~1.74%</t>
         </is>
       </c>
       <c r="Y61" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z61" s="3"/>
       <c r="AA61" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>广东省</t>
         </is>
       </c>
       <c r="AB61" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额为4亿元，募集资金将用于偿还发行人本部到期银行借款。</t>
+          <t>本期中期票据发行金额10亿元,拟偿还发行人有息负债</t>
         </is>
       </c>
       <c r="AC61" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,招商银行股份有限公司</t>
+          <t>招商银行股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD61" s="3"/>
@@ -13909,7 +13959,7 @@
       </c>
       <c r="AH61" s="3" t="inlineStr">
         <is>
-          <t>福建省国有资产管理有限公司2026年度第一期中期票据</t>
+          <t>广东省铁路建设投资集团有限公司2026年度第四期中期票据</t>
         </is>
       </c>
       <c r="AI61" s="3" t="inlineStr">
@@ -13940,32 +13990,32 @@
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP61" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ61" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">
         <is>
-          <t>其他非银</t>
+          <t>轨道交通</t>
         </is>
       </c>
       <c r="AT61" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>铁路运输</t>
         </is>
       </c>
       <c r="AU61" s="3" t="inlineStr">
@@ -13998,7 +14048,7 @@
     <row r="62" customHeight="true" ht="18.0">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>26蚌水01</t>
+          <t>26华光环保SCP017</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
@@ -14008,43 +14058,45 @@
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>283752.SH</t>
+          <t>012682170.IB</t>
         </is>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.59Y</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="F62" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.40 ~ 2.00</t>
         </is>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>25邕振V1</t>
+          <t>26华光环保SCP016</t>
         </is>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>3.67Y+5.00Y</t>
+          <t>218D</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>2.0916</t>
+          <t>1.5223</t>
         </is>
       </c>
       <c r="N62" s="3" t="inlineStr">
@@ -14054,12 +14106,12 @@
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>蚌埠靓淮河水利投资集团有限公司</t>
+          <t>无锡华光环保能源集团股份有限公司</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>C- 12.79</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14069,7 +14121,7 @@
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr">
@@ -14086,47 +14138,39 @@
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>2.08%~2.18%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z62" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z62" s="3"/>
       <c r="AA62" s="3" t="inlineStr">
         <is>
-          <t>安徽省-蚌埠市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB62" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将5亿元用于偿还到期公司债本金[23蚌水01]</t>
+          <t>本期超短期融资券拟发行1.00亿元，用于偿还发行人有息负债[26华光环保SCP006（科创债）]</t>
         </is>
       </c>
       <c r="AC62" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD62" s="3" t="inlineStr">
-        <is>
-          <t>蚌埠市国有资本运营控股集团有限公司</t>
-        </is>
-      </c>
+          <t>宁波银行股份有限公司,中国民生银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD62" s="3"/>
       <c r="AE62" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF62" s="3" t="inlineStr">
@@ -14136,78 +14180,78 @@
       </c>
       <c r="AG62" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH62" s="3" t="inlineStr">
         <is>
-          <t>蚌埠靓淮河水利投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>无锡华光环保能源集团股份有限公司2026年度第十七期超短期融资券</t>
         </is>
       </c>
       <c r="AI62" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ62" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2027-04-02</t>
         </is>
       </c>
       <c r="AK62" s="3"/>
       <c r="AL62" s="3" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ62" s="3" t="inlineStr">
+        <is>
+          <t>电力设备制造</t>
+        </is>
+      </c>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>其他电力设备</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>其他电力设备</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>专用设备</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM62" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AO62" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP62" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ62" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR62" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS62" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT62" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU62" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV62" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW62" s="3" t="inlineStr">
@@ -14230,7 +14274,7 @@
     <row r="63" customHeight="true" ht="18.0">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>26宜兴环保MTN001</t>
+          <t>26温州国投SCP002</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
@@ -14240,60 +14284,60 @@
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>102683429.IB</t>
+          <t>012682166.IB</t>
         </is>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>3.2</v>
+        <v>5.0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3.2</v>
+        <v>5.0</v>
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.50</t>
+          <t>1.20 ~ 1.80</t>
         </is>
       </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K63" s="3" t="inlineStr">
         <is>
-          <t>25宜兴环保MTN003</t>
+          <t>26温州国投SCP001</t>
         </is>
       </c>
       <c r="L63" s="3" t="inlineStr">
         <is>
-          <t>2.06Y+2.00Y</t>
+          <t>149D</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>1.7085</t>
+          <t>1.5326</t>
         </is>
       </c>
       <c r="N63" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4800</t>
         </is>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>江苏宜兴环保科技工业园发展集团有限公司</t>
+          <t>温州市国有资本投资运营有限公司</t>
         </is>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
-          <t>D- 2.97</t>
+          <t>D+ 8.93</t>
         </is>
       </c>
       <c r="Q63" s="3" t="inlineStr">
@@ -14320,39 +14364,39 @@
       <c r="V63" s="3"/>
       <c r="W63" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X63" s="3" t="inlineStr">
         <is>
-          <t>1.82%~1.92%</t>
+          <t>1.54%~1.58%</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z63" s="3"/>
       <c r="AA63" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB63" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行3.20亿元,募集资金将全部用于归还发行人本部债务融资工具本金[25宜兴环保SCP003]</t>
+          <t>本期超短期融资券拟发行金额为5亿元人民币,期限为270天,所募集资金用于偿还发行人及其下属子公司的银行流贷。</t>
         </is>
       </c>
       <c r="AC63" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司</t>
+          <t>杭州银行股份有限公司,中国光大银行股份有限公司</t>
         </is>
       </c>
       <c r="AD63" s="3"/>
       <c r="AE63" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF63" s="3" t="inlineStr">
@@ -14367,7 +14411,7 @@
       </c>
       <c r="AH63" s="3" t="inlineStr">
         <is>
-          <t>江苏宜兴环保科技工业园发展集团有限公司2026年度第一期中期票据</t>
+          <t>温州市国有资本投资运营有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI63" s="3" t="inlineStr">
@@ -14377,7 +14421,7 @@
       </c>
       <c r="AJ63" s="3" t="inlineStr">
         <is>
-          <t>2036-08-28</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="AK63" s="3"/>
@@ -14398,37 +14442,37 @@
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP63" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ63" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT63" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>饮料制造</t>
         </is>
       </c>
       <c r="AU63" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV63" s="3" t="inlineStr">
@@ -14438,7 +14482,7 @@
       </c>
       <c r="AW63" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX63" s="3" t="inlineStr">
@@ -14456,7 +14500,7 @@
     <row r="64" customHeight="true" ht="18.0">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>26舟交02</t>
+          <t>26桂国控SCP006</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
@@ -14466,43 +14510,45 @@
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>245968.SH</t>
+          <t>012682169.IB</t>
         </is>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F64" s="3"/>
+        <v>7.0</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.39 ~ 1.69</t>
         </is>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>26舟山交投MTN002</t>
+          <t>26桂国控SCP004</t>
         </is>
       </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>268D</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>1.8479</t>
+          <t>1.6094</t>
         </is>
       </c>
       <c r="N64" s="3" t="inlineStr">
@@ -14512,12 +14558,12 @@
       </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>舟山交通投资集团有限公司</t>
+          <t>广西国控资本运营集团有限责任公司</t>
         </is>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>C- 16.98</t>
+          <t>C- 15.75</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -14527,7 +14573,7 @@
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr">
@@ -14537,7 +14583,7 @@
       </c>
       <c r="T64" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U64" s="3"/>
@@ -14549,34 +14595,34 @@
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.53%~1.57%</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z64" s="3"/>
       <c r="AA64" s="3" t="inlineStr">
         <is>
-          <t>浙江省-舟山市</t>
+          <t>广西壮族自治区</t>
         </is>
       </c>
       <c r="AB64" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,发行人拟将6亿元用于偿还到期的公司债券本金[21舟交02]</t>
+          <t>本期债务融资工具募集资金全部用于归还发行人本部及下属公司的有息债务。</t>
         </is>
       </c>
       <c r="AC64" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,中信建投证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD64" s="3"/>
       <c r="AE64" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF64" s="3" t="inlineStr">
@@ -14586,12 +14632,12 @@
       </c>
       <c r="AG64" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH64" s="3" t="inlineStr">
         <is>
-          <t>舟山交通投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>广西国控资本运营集团有限责任公司2026年度第六期超短期融资券</t>
         </is>
       </c>
       <c r="AI64" s="3" t="inlineStr">
@@ -14601,64 +14647,60 @@
       </c>
       <c r="AJ64" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK64" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-05-25</t>
+        </is>
+      </c>
+      <c r="AK64" s="3"/>
       <c r="AL64" s="3" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr">
+        <is>
+          <t>农林牧渔</t>
+        </is>
+      </c>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>综合农林牧渔</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM64" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AO64" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ64" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR64" s="3" t="inlineStr">
-        <is>
-          <t>其他交运基础设施</t>
-        </is>
-      </c>
-      <c r="AS64" s="3" t="inlineStr">
-        <is>
-          <t>其他交运基础设施</t>
-        </is>
-      </c>
-      <c r="AT64" s="3" t="inlineStr">
-        <is>
-          <t>航运</t>
-        </is>
-      </c>
-      <c r="AU64" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV64" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -14679,12 +14721,14 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ64" s="3"/>
+      <c r="AZ64" s="4" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>26合高02</t>
+          <t>26闽国资MTN001</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
@@ -14694,7 +14738,7 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>283816.SH</t>
+          <t>102683420.IB</t>
         </is>
       </c>
       <c r="D65" s="3" t="inlineStr">
@@ -14703,49 +14747,51 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F65" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.40 ~ 2.10</t>
         </is>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
-          <t>26合高01</t>
+          <t>25闽国资MTN002(科创债)</t>
         </is>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>2.06Y</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>1.7772</t>
+          <t>1.6898</t>
         </is>
       </c>
       <c r="N65" s="3" t="inlineStr">
         <is>
-          <t>1.7900/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>合肥高新控股集团有限公司</t>
+          <t>福建省国有资产管理有限公司</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>A- 61.67</t>
+          <t>C- 24.45</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -14755,7 +14801,7 @@
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>08-27 16:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr">
@@ -14765,19 +14811,19 @@
       </c>
       <c r="T65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
       <c r="W65" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.66%~1.76%</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -14788,23 +14834,23 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB65" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金总额不超过5亿元。扣除发行费用后拟全部用于偿还到期公司债券本金[23 合高K1]</t>
+          <t>发行人本期中期票据发行金额为4亿元，募集资金将用于偿还发行人本部到期银行借款。</t>
         </is>
       </c>
       <c r="AC65" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信银行股份有限公司,招商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD65" s="3"/>
       <c r="AE65" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF65" s="3" t="inlineStr">
@@ -14814,28 +14860,28 @@
       </c>
       <c r="AG65" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH65" s="3" t="inlineStr">
         <is>
-          <t>合肥高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>福建省国有资产管理有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI65" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ65" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK65" s="3"/>
       <c r="AL65" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM65" s="3" t="inlineStr">
@@ -14845,37 +14891,37 @@
       </c>
       <c r="AN65" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP65" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ65" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他非银</t>
         </is>
       </c>
       <c r="AT65" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU65" s="3" t="inlineStr">
@@ -14908,7 +14954,7 @@
     <row r="66" customHeight="true" ht="18.0">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>26工业02</t>
+          <t>26宜兴环保MTN001</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
@@ -14918,21 +14964,23 @@
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>283719.SH</t>
+          <t>102683429.IB</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="F66" s="3"/>
+        <v>3.2</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>3.2</v>
+      </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.20</t>
+          <t>1.80 ~ 2.50</t>
         </is>
       </c>
       <c r="H66" s="3"/>
@@ -14944,32 +14992,32 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>26工业01</t>
+          <t>25宜兴环保MTN003</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>4.57Y</t>
+          <t>2.06Y+2.00Y</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>1.8763</t>
+          <t>1.7085</t>
         </is>
       </c>
       <c r="N66" s="3" t="inlineStr">
         <is>
-          <t>--/1.9000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>济南工业投资控股集团有限公司</t>
+          <t>江苏宜兴环保科技工业园发展集团有限公司</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>D- 1.36</t>
+          <t>D- 2.97</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -14979,7 +15027,7 @@
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr">
@@ -14996,7 +15044,7 @@
       <c r="V66" s="3"/>
       <c r="W66" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X66" s="3" t="inlineStr">
@@ -15006,29 +15054,29 @@
       </c>
       <c r="Y66" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z66" s="3"/>
       <c r="AA66" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB66" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟将不超过4.50亿元用于偿还到期债务;不超过1.50亿元用于生产性支出,具体为向济南工控资本有限公司(简称“工控资本”)权益出资。</t>
+          <t>发行人本期中期票据发行3.20亿元,募集资金将全部用于归还发行人本部债务融资工具本金[25宜兴环保SCP003]</t>
         </is>
       </c>
       <c r="AC66" s="3" t="inlineStr">
         <is>
-          <t>五矿证券有限公司,申万宏源证券有限公司</t>
+          <t>宁波银行股份有限公司</t>
         </is>
       </c>
       <c r="AD66" s="3"/>
       <c r="AE66" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF66" s="3" t="inlineStr">
@@ -15038,28 +15086,28 @@
       </c>
       <c r="AG66" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH66" s="3" t="inlineStr">
         <is>
-          <t>济南工业投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>江苏宜兴环保科技工业园发展集团有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI66" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ66" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2036-08-28</t>
         </is>
       </c>
       <c r="AK66" s="3"/>
       <c r="AL66" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM66" s="3" t="inlineStr">
@@ -15074,33 +15122,37 @@
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP66" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP66" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ66" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT66" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU66" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AV66" s="3" t="inlineStr">
@@ -15110,7 +15162,7 @@
       </c>
       <c r="AW66" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX66" s="3" t="inlineStr">
@@ -15128,17 +15180,17 @@
     <row r="67" customHeight="true" ht="18.0">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>26金城02</t>
+          <t>26合高02</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>283812.SH</t>
+          <t>283816.SH</t>
         </is>
       </c>
       <c r="D67" s="3" t="inlineStr">
@@ -15155,16 +15207,20 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
+      <c r="H67" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I67" s="4" t="n">
+        <v>45.49</v>
+      </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
-          <t>26金城01</t>
+          <t>26合高01</t>
         </is>
       </c>
       <c r="L67" s="3" t="inlineStr">
@@ -15174,22 +15230,22 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>1.7301</t>
+          <t>1.7740</t>
         </is>
       </c>
       <c r="N67" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/--</t>
         </is>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>张家港市金城投资发展集团有限公司</t>
+          <t>合肥高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
-          <t>C- 18.34</t>
+          <t>A- 70.00</t>
         </is>
       </c>
       <c r="Q67" s="3" t="inlineStr">
@@ -15199,7 +15255,7 @@
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 16:00</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
@@ -15216,12 +15272,12 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y67" s="3" t="inlineStr">
@@ -15232,17 +15288,17 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB67" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[23 金城04]</t>
+          <t>本期债券的募集资金总额不超过5亿元。扣除发行费用后拟全部用于偿还到期公司债券本金[23 合高K1]</t>
         </is>
       </c>
       <c r="AC67" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,国金证券股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD67" s="3"/>
@@ -15263,7 +15319,7 @@
       </c>
       <c r="AH67" s="3" t="inlineStr">
         <is>
-          <t>张家港市金城投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>合肥高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI67" s="3" t="inlineStr">
@@ -15294,27 +15350,27 @@
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP67" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR67" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS67" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT67" s="3" t="inlineStr">
@@ -15352,17 +15408,17 @@
     <row r="68" customHeight="true" ht="18.0">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>26万盛01</t>
+          <t>26工业02</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>283784.SH</t>
+          <t>283719.SH</t>
         </is>
       </c>
       <c r="D68" s="3" t="inlineStr">
@@ -15376,44 +15432,48 @@
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
+          <t>1.70 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>47.85</v>
+      </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>25万盛04</t>
+          <t>26工业01</t>
         </is>
       </c>
       <c r="L68" s="3" t="inlineStr">
         <is>
-          <t>4.29Y</t>
+          <t>4.57Y</t>
         </is>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>2.3187</t>
+          <t>1.8796</t>
         </is>
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8900</t>
         </is>
       </c>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>重庆市万盛经济技术开发区开发投资集团有限公司</t>
+          <t>济南工业投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>B- 47.07</t>
+          <t>C- 17.73</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -15440,33 +15500,33 @@
       <c r="V68" s="3"/>
       <c r="W68" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X68" s="3" t="inlineStr">
         <is>
-          <t>2.46%~2.56%</t>
+          <t>1.82%~1.92%</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z68" s="3"/>
       <c r="AA68" s="3" t="inlineStr">
         <is>
-          <t>重庆市-重庆市万盛经济技术开发区</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB68" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟发行规模为不超过6.00亿元(含6.00亿元)，募集资金扣除发行费用后，拟用于偿还公司到期的公司债券本金[24万盛01,23万盛05]</t>
+          <t>本期债券募集资金扣除发行费用后,拟将不超过4.50亿元用于偿还到期债务;不超过1.50亿元用于生产性支出,具体为向济南工控资本有限公司(简称“工控资本”)权益出资。</t>
         </is>
       </c>
       <c r="AC68" s="3" t="inlineStr">
         <is>
-          <t>华源证券股份有限公司</t>
+          <t>五矿证券有限公司,申万宏源证券有限公司</t>
         </is>
       </c>
       <c r="AD68" s="3"/>
@@ -15487,7 +15547,7 @@
       </c>
       <c r="AH68" s="3" t="inlineStr">
         <is>
-          <t>重庆市万盛经济技术开发区开发投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>济南工业投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI68" s="3" t="inlineStr">
@@ -15518,32 +15578,28 @@
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP68" s="3"/>
       <c r="AQ68" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR68" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS68" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT68" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU68" s="3" t="inlineStr">
@@ -15576,49 +15632,57 @@
     <row r="69" customHeight="true" ht="18.0">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>26溧水经开PPN010</t>
+          <t>26万盛01</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
-        </is>
-      </c>
-      <c r="C69" s="3"/>
+          <t>08-27 19:00</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>283784.SH</t>
+        </is>
+      </c>
       <c r="D69" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.30</t>
-        </is>
-      </c>
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>93.85</v>
+      </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
-          <t>26溧水经开PPN008</t>
+          <t>25万盛04</t>
         </is>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>2.84Y</t>
+          <t>4.29Y</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>1.7840</t>
+          <t>2.3229</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -15628,12 +15692,12 @@
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>南京溧水经济技术开发集团有限公司</t>
+          <t>重庆市万盛经济技术开发区开发投资集团有限公司</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>C- 16.25</t>
+          <t>B- 42.89</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -15643,7 +15707,7 @@
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr">
@@ -15660,39 +15724,39 @@
       <c r="V69" s="3"/>
       <c r="W69" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>1.79%~1.89%</t>
+          <t>2.46%~2.56%</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z69" s="3"/>
       <c r="AA69" s="3" t="inlineStr">
         <is>
-          <t>江苏省-南京市</t>
+          <t>重庆市-重庆市万盛经济技术开发区</t>
         </is>
       </c>
       <c r="AB69" s="3" t="inlineStr">
         <is>
-          <t>本期发行金额人民币5亿元,募集资金将全部用于偿还发行人本部存量债务融资工具本金[24溧水经开PPN006]</t>
+          <t>本期债券拟发行规模为不超过6.00亿元(含6.00亿元)，募集资金扣除发行费用后，拟用于偿还公司到期的公司债券本金[24万盛01,23万盛05]</t>
         </is>
       </c>
       <c r="AC69" s="3" t="inlineStr">
         <is>
-          <t>南京银行股份有限公司</t>
+          <t>华源证券股份有限公司</t>
         </is>
       </c>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF69" s="3" t="inlineStr">
@@ -15702,12 +15766,12 @@
       </c>
       <c r="AG69" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH69" s="3" t="inlineStr">
         <is>
-          <t>南京溧水经济技术开发集团有限公司2026年度第十期定向债务融资工具</t>
+          <t>重庆市万盛经济技术开发区开发投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI69" s="3" t="inlineStr">
@@ -15717,13 +15781,13 @@
       </c>
       <c r="AJ69" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK69" s="3"/>
       <c r="AL69" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AM69" s="3" t="inlineStr">
@@ -15791,14 +15855,12 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ69" s="4" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="AZ69" s="3"/>
     </row>
     <row r="70" customHeight="true" ht="18.0">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>26南电GN007(科创债)</t>
+          <t>26溧水经开PPN010</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
@@ -15806,62 +15868,56 @@
           <t>08-27 18:00</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>132680090.IB</t>
-        </is>
-      </c>
+      <c r="C70" s="3"/>
       <c r="D70" s="3" t="inlineStr">
         <is>
-          <t>4.99Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="F70" s="4" t="n">
-        <v>15.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F70" s="3"/>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.90</t>
+          <t>1.60 ~ 2.30</t>
         </is>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
       <c r="J70" s="3" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>26南电MTN004</t>
+          <t>26溧水经开PPN008</t>
         </is>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>4.90Y</t>
+          <t>2.84Y</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1.7111</t>
+          <t>1.7840</t>
         </is>
       </c>
       <c r="N70" s="3" t="inlineStr">
         <is>
-          <t>1.7300/1.7100</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司</t>
+          <t>南京溧水经济技术开发集团有限公司</t>
         </is>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>B- 39.08</t>
+          <t>C- 16.68</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -15888,44 +15944,44 @@
       <c r="V70" s="3"/>
       <c r="W70" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.79%~1.89%</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z70" s="3"/>
       <c r="AA70" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-南京市</t>
         </is>
       </c>
       <c r="AB70" s="3" t="inlineStr">
         <is>
-          <t>本期绿色科技创新债券发行规模15亿元，募集资金计划全部用于发行人下属子公司城镇电力设施智能化建设和改造、智能电网建设和运营项目，其中贵州电网有限责任公司8亿元、云南电网有限责任公司2亿元、广西电网有限责任公司5亿元</t>
+          <t>本期发行金额人民币5亿元,募集资金将全部用于偿还发行人本部存量债务融资工具本金[24溧水经开PPN006]</t>
         </is>
       </c>
       <c r="AC70" s="3" t="inlineStr">
         <is>
-          <t>中国银行股份有限公司,中国建设银行股份有限公司</t>
+          <t>南京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD70" s="3"/>
       <c r="AE70" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF70" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG70" s="3" t="inlineStr">
@@ -15935,17 +15991,17 @@
       </c>
       <c r="AH70" s="3" t="inlineStr">
         <is>
-          <t>中国南方电网有限责任公司2026年度第七期绿色科技创新债券</t>
+          <t>南京溧水经济技术开发集团有限公司2026年度第十期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI70" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ70" s="3" t="inlineStr">
         <is>
-          <t>2031-08-22</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK70" s="3"/>
@@ -15966,32 +16022,32 @@
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP70" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ70" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT70" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU70" s="3" t="inlineStr">
@@ -16019,12 +16075,14 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ70" s="3"/>
+      <c r="AZ70" s="4" t="n">
+        <v>0.003</v>
+      </c>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN001(资产担保)</t>
+          <t>26南电GN007(科创债)</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
@@ -16034,60 +16092,60 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>102683428.IB</t>
+          <t>132680090.IB</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>4.99Y</t>
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.79</t>
+          <t>1.50 ~ 1.90</t>
         </is>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN002</t>
+          <t>26南电MTN004</t>
         </is>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>2.87Y</t>
+          <t>4.90Y</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>1.7766</t>
+          <t>1.7111</t>
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7400/1.7000</t>
         </is>
       </c>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司</t>
+          <t>中国南方电网有限责任公司</t>
         </is>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>C- 16.25</t>
+          <t>B- 39.14</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16114,44 +16172,44 @@
       <c r="V71" s="3"/>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X71" s="3"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y71" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z71" s="3"/>
       <c r="AA71" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB71" s="3" t="inlineStr">
         <is>
-          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币,用于偿还金融机构借款</t>
+          <t>本期绿色科技创新债券发行规模15亿元，募集资金计划全部用于发行人下属子公司城镇电力设施智能化建设和改造、智能电网建设和运营项目，其中贵州电网有限责任公司8亿元、云南电网有限责任公司2亿元、广西电网有限责任公司5亿元</t>
         </is>
       </c>
       <c r="AC71" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD71" s="3" t="inlineStr">
-        <is>
-          <t>温州交运集团房地产投资开发有限公司</t>
-        </is>
-      </c>
+          <t>中国银行股份有限公司,中国建设银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD71" s="3"/>
       <c r="AE71" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF71" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG71" s="3" t="inlineStr">
@@ -16161,7 +16219,7 @@
       </c>
       <c r="AH71" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
+          <t>中国南方电网有限责任公司2026年度第七期绿色科技创新债券</t>
         </is>
       </c>
       <c r="AI71" s="3" t="inlineStr">
@@ -16171,7 +16229,7 @@
       </c>
       <c r="AJ71" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2031-08-22</t>
         </is>
       </c>
       <c r="AK71" s="3"/>
@@ -16197,27 +16255,27 @@
       </c>
       <c r="AP71" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ71" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>公用事业</t>
         </is>
       </c>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>其他电力</t>
         </is>
       </c>
       <c r="AT71" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="AU71" s="3" t="inlineStr">
@@ -16227,7 +16285,7 @@
       </c>
       <c r="AV71" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW71" s="3" t="inlineStr">
@@ -16250,68 +16308,70 @@
     <row r="72" customHeight="true" ht="18.0">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>26太新Y7</t>
+          <t>26温州交运MTN001(资产担保)</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>08-27 19:00</t>
+          <t>08-27 18:00</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
         <is>
-          <t>245995.SH</t>
+          <t>102683428.IB</t>
         </is>
       </c>
       <c r="D72" s="3" t="inlineStr">
         <is>
-          <t>7+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="F72" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.50 ~ 1.79</t>
         </is>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
       <c r="J72" s="3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>26太新Y6</t>
+          <t>26温州交运MTN002</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>6.98Y+N</t>
+          <t>2.87Y</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>2.2235</t>
+          <t>1.7766</t>
         </is>
       </c>
       <c r="N72" s="3" t="inlineStr">
         <is>
-          <t>2.2300/2.2150</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>温州市交通运输集团有限公司</t>
         </is>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
-          <t>B- 38.74</t>
+          <t>C- 16.25</t>
         </is>
       </c>
       <c r="Q72" s="3" t="inlineStr">
@@ -16321,7 +16381,7 @@
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -16331,46 +16391,46 @@
       </c>
       <c r="T72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U72" s="3"/>
       <c r="V72" s="3"/>
       <c r="W72" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X72" s="3" t="inlineStr">
-        <is>
-          <t>2.37%~2.47%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X72" s="3"/>
       <c r="Y72" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z72" s="3"/>
       <c r="AA72" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB72" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券的本金[24太新Y1]</t>
+          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币,用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC72" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信证券股份有限公司,国联民生证券承销保荐有限公司,东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD72" s="3"/>
+          <t>浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD72" s="3" t="inlineStr">
+        <is>
+          <t>温州交运集团房地产投资开发有限公司</t>
+        </is>
+      </c>
       <c r="AE72" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF72" s="3" t="inlineStr">
@@ -16380,12 +16440,12 @@
       </c>
       <c r="AG72" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH72" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年面向专业投资者公开发行可续期公司债券(第四期)</t>
+          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具</t>
         </is>
       </c>
       <c r="AI72" s="3" t="inlineStr">
@@ -16395,68 +16455,68 @@
       </c>
       <c r="AJ72" s="3" t="inlineStr">
         <is>
-          <t>2033-09-01</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK72" s="3"/>
       <c r="AL72" s="3" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AM72" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN72" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AO72" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP72" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ72" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR72" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>公交</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM72" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN72" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO72" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP72" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ72" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR72" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS72" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT72" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU72" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV72" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW72" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX72" s="3" t="inlineStr">
@@ -16474,7 +16534,7 @@
     <row r="73" customHeight="true" ht="18.0">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>26平发02</t>
+          <t>26太新Y7</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
@@ -16484,58 +16544,62 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>283855.SH</t>
+          <t>245995.SH</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7+N</t>
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>4.0</v>
+        <v>9.0</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I73" s="4" t="n">
+        <v>71.36</v>
+      </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>26平发01</t>
+          <t>26太新Y6</t>
         </is>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>4.41Y</t>
+          <t>6.98Y+N</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>2.1008</t>
+          <t>2.2233</t>
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.2150</t>
         </is>
       </c>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>平顶山发展投资控股集团有限公司</t>
+          <t>无锡市太湖新城发展集团有限公司</t>
         </is>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>C 27.71</t>
+          <t>B- 41.67</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -16555,36 +16619,40 @@
       </c>
       <c r="T73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U73" s="3"/>
       <c r="V73" s="3"/>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X73" s="3"/>
+          <t>4-</t>
+        </is>
+      </c>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>2.37%~2.47%</t>
+        </is>
+      </c>
       <c r="Y73" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z73" s="3"/>
       <c r="AA73" s="3" t="inlineStr">
         <is>
-          <t>河南省-平顶山市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB73" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[25平发D2]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券的本金[24太新Y1]</t>
         </is>
       </c>
       <c r="AC73" s="3" t="inlineStr">
         <is>
-          <t>国联民生证券承销保荐有限公司,华创证券有限责任公司</t>
+          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信证券股份有限公司,国联民生证券承销保荐有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD73" s="3"/>
@@ -16605,24 +16673,20 @@
       </c>
       <c r="AH73" s="3" t="inlineStr">
         <is>
-          <t>平顶山发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种一)</t>
+          <t>无锡市太湖新城发展集团有限公司2026年面向专业投资者公开发行可续期公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI73" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ73" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK73" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2033-09-01</t>
+        </is>
+      </c>
+      <c r="AK73" s="3"/>
       <c r="AL73" s="3" t="inlineStr">
         <is>
           <t/>
@@ -16635,7 +16699,7 @@
       </c>
       <c r="AN73" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO73" s="3" t="inlineStr">
@@ -16650,17 +16714,17 @@
       </c>
       <c r="AQ73" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR73" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS73" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT73" s="3" t="inlineStr">
@@ -16680,7 +16744,7 @@
       </c>
       <c r="AW73" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX73" s="3" t="inlineStr">
@@ -16698,7 +16762,7 @@
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26平发03</t>
+          <t>26平发02</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -16708,12 +16772,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>283856.SH</t>
+          <t>283855.SH</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
@@ -16722,14 +16786,14 @@
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.20</t>
+          <t>2.00 ~ 2.60</t>
         </is>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
@@ -16744,7 +16808,7 @@
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>2.1008</t>
+          <t>2.0994</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
@@ -16759,7 +16823,7 @@
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>C 27.71</t>
+          <t>C 25.44</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -16829,7 +16893,7 @@
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>平顶山发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)</t>
+          <t>平顶山发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种一)</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
@@ -16839,10 +16903,14 @@
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>2033-08-31</t>
-        </is>
-      </c>
-      <c r="AK74" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK74" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL74" s="3" t="inlineStr">
         <is>
           <t/>
@@ -16918,7 +16986,7 @@
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26国新01</t>
+          <t>26平发03</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -16928,58 +16996,58 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>245985.SH</t>
+          <t>283856.SH</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
+          <t>2.50 ~ 3.20</t>
         </is>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>21国新控股MTN002</t>
+          <t>26平发01</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>4.41Y</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1.7413</t>
+          <t>2.0994</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>1.7600/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>中国国新控股有限责任公司</t>
+          <t>平顶山发展投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>A- 67.15</t>
+          <t>C 25.44</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -16999,40 +17067,36 @@
       </c>
       <c r="T75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U75" s="3"/>
       <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X75" s="3" t="inlineStr">
-        <is>
-          <t>1.69%~1.79%</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X75" s="3"/>
       <c r="Y75" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河南省-平顶山市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于生产性支出,包括但不限于补充流动资金、偿还有息债务等符合法律法规及监管要求的用途</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[25平发D2]</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,国新证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
+          <t>国联民生证券承销保荐有限公司,华创证券有限责任公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
@@ -17043,7 +17107,7 @@
       </c>
       <c r="AF75" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG75" s="3" t="inlineStr">
@@ -17053,17 +17117,17 @@
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>中国国新控股有限责任公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>平顶山发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2033-08-31</t>
         </is>
       </c>
       <c r="AK75" s="3"/>
@@ -17079,17 +17143,17 @@
       </c>
       <c r="AN75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP75" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ75" s="3" t="inlineStr">
@@ -17099,17 +17163,17 @@
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-27.xlsx
+++ b/data/credit_bond_all_2026-08-27.xlsx
@@ -945,8 +945,12 @@
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>88.85</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2.07</t>
@@ -1002,7 +1006,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>1.67</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
@@ -1133,9 +1139,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ4" s="3"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1169,8 +1173,12 @@
           <t>1.70 ~ 2.30</t>
         </is>
       </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+      <c r="H5" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>57.49</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>1.83</t>
@@ -1226,8 +1234,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
+      <c r="U5" s="4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>7.0</v>
+      </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
           <t>7+</t>
@@ -1395,8 +1407,12 @@
           <t>1.70 ~ 2.00</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>63.49</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.78</t>
@@ -1621,8 +1637,12 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>79.85</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>2.14</t>
@@ -1678,7 +1698,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
+      <c r="U7" s="4" t="n">
+        <v>2.61</v>
+      </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
@@ -1750,7 +1772,7 @@
       </c>
       <c r="AM7" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AN7" s="3" t="inlineStr">
@@ -1847,8 +1869,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+      <c r="H8" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>58.85</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
           <t>1.97</t>
@@ -1904,8 +1930,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="U8" s="4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -2039,9 +2069,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ8" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ8" s="3"/>
     </row>
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
@@ -2075,8 +2103,12 @@
           <t>1.60 ~ 2.20</t>
         </is>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="H9" s="4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>54.49</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
           <t>1.85</t>
@@ -2132,7 +2164,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U9" s="3"/>
+      <c r="U9" s="4" t="n">
+        <v>5.14</v>
+      </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
@@ -2271,9 +2305,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ9" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ9" s="3"/>
     </row>
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
@@ -2307,8 +2339,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>66.49</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>1.93</t>
@@ -2364,8 +2400,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="V10" s="4" t="n">
+        <v>1.45</v>
+      </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -2499,9 +2539,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ10" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ10" s="3"/>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
@@ -2535,8 +2573,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
+      <c r="H11" s="4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>101.85</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
           <t>2.44</t>
@@ -2985,8 +3027,12 @@
           <t>1.80 ~ 2.20</t>
         </is>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="H13" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>29.12</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
           <t>2.04</t>
@@ -3042,7 +3088,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U13" s="3"/>
+      <c r="U13" s="4" t="n">
+        <v>1.34</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
@@ -3437,8 +3485,12 @@
           <t>1.90 ~ 2.50</t>
         </is>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="H15" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>99.6</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
           <t>2.28</t>
@@ -3494,8 +3546,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
+      <c r="U15" s="4" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>23.0</v>
+      </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -3889,8 +3945,12 @@
           <t>1.47 ~ 1.67</t>
         </is>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+      <c r="H17" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>31.49</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -3947,7 +4007,9 @@
         </is>
       </c>
       <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
+      <c r="V17" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -4115,8 +4177,12 @@
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+      <c r="H18" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>78.85</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
           <t>2.36</t>
@@ -4172,7 +4238,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U18" s="3"/>
+      <c r="U18" s="4" t="n">
+        <v>4.68</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
@@ -4349,8 +4417,12 @@
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="H19" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>23.38</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
           <t>1.47</t>
@@ -4406,8 +4478,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
+      <c r="U19" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>6.9</v>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -4541,9 +4617,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ19" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ19" s="3"/>
     </row>
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
@@ -4577,8 +4651,12 @@
           <t>1.60 ~ 2.10</t>
         </is>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
+      <c r="H20" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>36.36</v>
+      </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -4634,8 +4712,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
+      <c r="U20" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V20" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -5033,8 +5115,12 @@
           <t>1.30 ~ 1.55</t>
         </is>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
+      <c r="H22" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>32.31</v>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -5090,8 +5176,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="V22" s="4" t="n">
+        <v>4.24</v>
+      </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
           <t>4</t>
@@ -5225,9 +5315,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ22" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ22" s="3"/>
     </row>
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
@@ -5489,8 +5577,12 @@
           <t>1.30 ~ 1.60</t>
         </is>
       </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
+      <c r="H24" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>23.38</v>
+      </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
           <t>1.47</t>
@@ -5546,8 +5638,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
+      <c r="U24" s="4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="V24" s="4" t="n">
+        <v>5.2</v>
+      </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
           <t>3</t>
@@ -5681,9 +5777,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ24" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ24" s="3"/>
     </row>
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
@@ -5717,8 +5811,12 @@
           <t>1.60 ~ 2.30</t>
         </is>
       </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
+      <c r="H25" s="4" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>57.49</v>
+      </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
           <t>1.88</t>
@@ -5774,8 +5872,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
+      <c r="U25" s="4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V25" s="4" t="n">
+        <v>1.06</v>
+      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
           <t>7+</t>
@@ -5909,9 +6011,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ25" s="4" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="AZ25" s="3"/>
     </row>
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
@@ -5945,8 +6045,12 @@
           <t>1.30 ~ 1.50</t>
         </is>
       </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
+      <c r="H26" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>19.31</v>
+      </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
           <t>1.46</t>
@@ -6199,7 +6303,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8000/1.7600</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
@@ -6427,7 +6531,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t>2.0200/--</t>
+          <t>1.9900/1.9700</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
@@ -6635,8 +6739,12 @@
           <t>1.55 ~ 1.85</t>
         </is>
       </c>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
+      <c r="H29" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>46.17</v>
+      </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
           <t>1.70</t>
@@ -6692,8 +6800,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
+      <c r="U29" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>2.74</v>
+      </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
           <t>6-</t>
@@ -6861,8 +6973,12 @@
           <t>1.40 ~ 2.00</t>
         </is>
       </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
+      <c r="H30" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>45.49</v>
+      </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
           <t>1.67</t>
@@ -6918,7 +7034,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U30" s="3"/>
+      <c r="U30" s="4" t="n">
+        <v>3.57</v>
+      </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
@@ -7081,8 +7199,12 @@
           <t>1.80 ~ 2.40</t>
         </is>
       </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
+      <c r="H31" s="4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>63.85</v>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t>2.06</t>
@@ -7761,8 +7883,12 @@
           <t>1.50 ~ 2.50</t>
         </is>
       </c>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
+      <c r="H34" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>20.85</v>
+      </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
           <t>1.69</t>
@@ -7985,8 +8111,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
+      <c r="H35" s="4" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>29.6</v>
+      </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
           <t>1.58</t>
@@ -8042,7 +8172,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U35" s="3"/>
+      <c r="U35" s="4" t="n">
+        <v>1.56</v>
+      </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
@@ -8201,8 +8333,12 @@
           <t>1.60 ~ 2.10</t>
         </is>
       </c>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
+      <c r="H36" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>51.49</v>
+      </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
           <t>1.78</t>
@@ -8258,8 +8394,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
+      <c r="U36" s="4" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>2.5</v>
+      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
           <t>6</t>
@@ -8421,8 +8561,12 @@
           <t>1.60 ~ 2.70</t>
         </is>
       </c>
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
+      <c r="H37" s="4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>82.85</v>
+      </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
           <t>2.21</t>
@@ -8478,8 +8622,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
+      <c r="U37" s="4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>1.17</v>
+      </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
           <t>7-</t>
@@ -8613,9 +8761,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ37" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ37" s="3"/>
     </row>
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
@@ -8643,8 +8789,12 @@
           <t>1.40 ~ 2.40</t>
         </is>
       </c>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
+      <c r="H38" s="4" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>37.85</v>
+      </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
           <t>1.82</t>
@@ -8700,7 +8850,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U38" s="3"/>
+      <c r="U38" s="4" t="n">
+        <v>2.87</v>
+      </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
@@ -8867,8 +9019,12 @@
           <t>1.60 ~ 2.60</t>
         </is>
       </c>
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
+      <c r="H39" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>68.49</v>
+      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
           <t>1.86</t>
@@ -9087,8 +9243,12 @@
           <t>1.80 ~ 2.60</t>
         </is>
       </c>
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
+      <c r="H40" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>68.85</v>
+      </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
           <t>2.09</t>
@@ -9309,8 +9469,12 @@
           <t>2.00 ~ 2.30</t>
         </is>
       </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
+      <c r="H41" s="4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>18.12</v>
+      </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
           <t>2.17</t>
@@ -10724,7 +10888,9 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U47" s="3"/>
+      <c r="U47" s="4" t="n">
+        <v>5.87</v>
+      </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3" t="inlineStr">
         <is>
@@ -11092,7 +11258,7 @@
     <row r="49" customHeight="true" ht="18.0">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>26蚌水02</t>
+          <t>26蚌水02(取消发行)</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -11102,7 +11268,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>283758.SH</t>
+          <t>DY283758.SH</t>
         </is>
       </c>
       <c r="D49" s="3" t="inlineStr">
@@ -11235,7 +11401,7 @@
       </c>
       <c r="AH49" s="3" t="inlineStr">
         <is>
-          <t>蚌埠靓淮河水利投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)</t>
+          <t>蚌埠靓淮河水利投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI49" s="3" t="inlineStr">
@@ -11351,8 +11517,12 @@
           <t>1.70 ~ 2.70</t>
         </is>
       </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
+      <c r="H50" s="4" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>63.49</v>
+      </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
           <t>--</t>
@@ -12092,7 +12262,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U53" s="3"/>
+      <c r="U53" s="4" t="n">
+        <v>3.28</v>
+      </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3" t="inlineStr">
         <is>
@@ -12261,8 +12433,12 @@
           <t>1.90 ~ 2.40</t>
         </is>
       </c>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
+      <c r="H54" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>83.49</v>
+      </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
           <t>2.31</t>
@@ -12318,7 +12494,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U54" s="3"/>
+      <c r="U54" s="4" t="n">
+        <v>1.85</v>
+      </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3" t="inlineStr">
         <is>
@@ -12487,8 +12665,12 @@
           <t>1.70 ~ 2.40</t>
         </is>
       </c>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
+      <c r="H55" s="4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I55" s="4" t="n">
+        <v>51.85</v>
+      </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
           <t>1.91</t>
@@ -12544,8 +12726,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
+      <c r="U55" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="V55" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W55" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -12713,8 +12899,12 @@
           <t>1.50 ~ 2.20</t>
         </is>
       </c>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
+      <c r="H56" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>38.85</v>
+      </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
           <t>1.85</t>
@@ -12770,8 +12960,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
+      <c r="U56" s="4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V56" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W56" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -12939,8 +13133,12 @@
           <t>1.60 ~ 1.90</t>
         </is>
       </c>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
+      <c r="H57" s="4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="I57" s="4" t="n">
+        <v>32.85</v>
+      </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -12996,7 +13194,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U57" s="3"/>
+      <c r="U57" s="4" t="n">
+        <v>3.44</v>
+      </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3" t="inlineStr">
         <is>
@@ -13131,9 +13331,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ57" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ57" s="3"/>
     </row>
     <row r="58" customHeight="true" ht="18.0">
       <c r="A58" s="3" t="inlineStr">
@@ -13167,8 +13365,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
+      <c r="H58" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I58" s="4" t="n">
+        <v>27.85</v>
+      </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
           <t>1.77</t>
@@ -13224,8 +13426,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U58" s="3"/>
-      <c r="V58" s="3"/>
+      <c r="U58" s="4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V58" s="4" t="n">
+        <v>8.0</v>
+      </c>
       <c r="W58" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -13393,8 +13599,12 @@
           <t>1.50 ~ 2.10</t>
         </is>
       </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
+      <c r="H59" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I59" s="4" t="n">
+        <v>53.49</v>
+      </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
           <t>1.76</t>
@@ -13450,8 +13660,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
+      <c r="U59" s="4" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="V59" s="4" t="n">
+        <v>4.31</v>
+      </c>
       <c r="W59" s="3" t="inlineStr">
         <is>
           <t>4+</t>
@@ -13589,9 +13803,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ59" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ59" s="3"/>
     </row>
     <row r="60" customHeight="true" ht="18.0">
       <c r="A60" s="3" t="inlineStr">
@@ -13851,8 +14063,12 @@
           <t>1.40 ~ 1.90</t>
         </is>
       </c>
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
+      <c r="H61" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I61" s="4" t="n">
+        <v>33.49</v>
+      </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
           <t>1.68</t>
@@ -13908,7 +14124,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U61" s="3"/>
+      <c r="U61" s="4" t="n">
+        <v>4.1</v>
+      </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3" t="inlineStr">
         <is>
@@ -14077,8 +14295,12 @@
           <t>1.40 ~ 2.00</t>
         </is>
       </c>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
+      <c r="H62" s="4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="I62" s="4" t="n">
+        <v>27.93</v>
+      </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -14134,7 +14356,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U62" s="3"/>
+      <c r="U62" s="4" t="n">
+        <v>1.7</v>
+      </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3" t="inlineStr">
         <is>
@@ -14303,8 +14527,12 @@
           <t>1.20 ~ 1.80</t>
         </is>
       </c>
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
+      <c r="H63" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>23.38</v>
+      </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -14360,8 +14588,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
+      <c r="U63" s="4" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="V63" s="4" t="n">
+        <v>1.08</v>
+      </c>
       <c r="W63" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -14529,8 +14761,12 @@
           <t>1.39 ~ 1.69</t>
         </is>
       </c>
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
+      <c r="H64" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>33.38</v>
+      </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
           <t>1.48</t>
@@ -14586,8 +14822,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U64" s="3"/>
-      <c r="V64" s="3"/>
+      <c r="U64" s="4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="V64" s="4" t="n">
+        <v>1.56</v>
+      </c>
       <c r="W64" s="3" t="inlineStr">
         <is>
           <t>5</t>
@@ -14721,9 +14961,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ64" s="4" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="AZ64" s="3"/>
     </row>
     <row r="65" customHeight="true" ht="18.0">
       <c r="A65" s="3" t="inlineStr">
@@ -14757,8 +14995,12 @@
           <t>1.40 ~ 2.10</t>
         </is>
       </c>
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
+      <c r="H65" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>39.49</v>
+      </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
           <t>1.77</t>
@@ -14815,7 +15057,9 @@
         </is>
       </c>
       <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
+      <c r="V65" s="4" t="n">
+        <v>1.08</v>
+      </c>
       <c r="W65" s="3" t="inlineStr">
         <is>
           <t>5-</t>
@@ -14983,8 +15227,12 @@
           <t>1.80 ~ 2.50</t>
         </is>
       </c>
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
+      <c r="H66" s="4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="I66" s="4" t="n">
+        <v>35.12</v>
+      </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
           <t>1.94</t>
@@ -15040,7 +15288,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U66" s="3"/>
+      <c r="U66" s="4" t="n">
+        <v>2.18</v>
+      </c>
       <c r="V66" s="3"/>
       <c r="W66" s="3" t="inlineStr">
         <is>
@@ -15883,8 +16133,12 @@
           <t>1.60 ~ 2.30</t>
         </is>
       </c>
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
+      <c r="H70" s="4" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>51.49</v>
+      </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
           <t>1.77</t>
@@ -15940,8 +16194,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
+      <c r="U70" s="4" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>1.1</v>
+      </c>
       <c r="W70" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -16075,9 +16333,7 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ70" s="4" t="n">
-        <v>0.003</v>
-      </c>
+      <c r="AZ70" s="3"/>
     </row>
     <row r="71" customHeight="true" ht="18.0">
       <c r="A71" s="3" t="inlineStr">
@@ -16111,8 +16367,12 @@
           <t>1.50 ~ 1.90</t>
         </is>
       </c>
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
+      <c r="H71" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>18.85</v>
+      </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
           <t>1.66</t>
@@ -16168,8 +16428,12 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U71" s="3"/>
-      <c r="V71" s="3"/>
+      <c r="U71" s="4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="V71" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="W71" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -16986,7 +17250,7 @@
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26平发03</t>
+          <t>26七匹狼MTN001(科创债)</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
@@ -16996,25 +17260,31 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>283856.SH</t>
+          <t>102683419.IB</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>7Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F75" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2.50 ~ 3.20</t>
-        </is>
-      </c>
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>83.49</v>
+      </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
           <t>2.50</t>
@@ -17022,17 +17292,17 @@
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>26平发01</t>
+          <t>25朗姿MTN001</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>4.41Y</t>
+          <t>3.40Y</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>2.0994</t>
+          <t>2.6931</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
@@ -17042,14 +17312,10 @@
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>平顶山发展投资控股集团有限公司</t>
-        </is>
-      </c>
-      <c r="P75" s="3" t="inlineStr">
-        <is>
-          <t>C 25.44</t>
-        </is>
-      </c>
+          <t>福建七匹狼集团有限公司</t>
+        </is>
+      </c>
+      <c r="P75" s="3"/>
       <c r="Q75" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -17057,7 +17323,7 @@
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -17067,16 +17333,16 @@
       </c>
       <c r="T75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="U75" s="3"/>
-      <c r="V75" s="3"/>
-      <c r="W75" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="U75" s="4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V75" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W75" s="3"/>
       <c r="X75" s="3"/>
       <c r="Y75" s="3" t="inlineStr">
         <is>
@@ -17086,54 +17352,54 @@
       <c r="Z75" s="3"/>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>河南省-平顶山市</t>
+          <t>福建省-泉州市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[25平发D2]</t>
+          <t>本次发行金额3亿元,用于直接投资或基金出资置换,对科技型企业提供股性资金支持,及偿还发行人本部有息债务。</t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>国联民生证券承销保荐有限公司,华创证券有限责任公司</t>
+          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司,厦门银行股份有限公司,浙商银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF75" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG75" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>平顶山发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)</t>
+          <t>福建七匹狼集团有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2033-08-31</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK75" s="3"/>
       <c r="AL75" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM75" s="3" t="inlineStr">
@@ -17143,37 +17409,33 @@
       </c>
       <c r="AN75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP75" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP75" s="3"/>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>轻工制造</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>纺织服饰</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>纺织服饰</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>服装家纺</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">
@@ -17206,7 +17468,7 @@
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26七匹狼MTN001(科创债)</t>
+          <t>26平发03</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
@@ -17216,27 +17478,29 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>102683419.IB</t>
+          <t>283856.SH</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>7Y</t>
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F76" s="4" t="n">
-        <v>3.0</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="F76" s="3"/>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
+          <t>2.50 ~ 3.20</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>102.36</v>
+      </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
           <t>2.50</t>
@@ -17244,17 +17508,17 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>25朗姿MTN001</t>
+          <t>26平发01</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>3.40Y</t>
+          <t>4.41Y</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>2.6931</t>
+          <t>2.0994</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
@@ -17264,10 +17528,14 @@
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>福建七匹狼集团有限公司</t>
-        </is>
-      </c>
-      <c r="P76" s="3"/>
+          <t>平顶山发展投资控股集团有限公司</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>C 25.44</t>
+        </is>
+      </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
           <t>2026-08-27</t>
@@ -17275,7 +17543,7 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr">
@@ -17285,12 +17553,16 @@
       </c>
       <c r="T76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
-      <c r="W76" s="3"/>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="X76" s="3"/>
       <c r="Y76" s="3" t="inlineStr">
         <is>
@@ -17300,90 +17572,94 @@
       <c r="Z76" s="3"/>
       <c r="AA76" s="3" t="inlineStr">
         <is>
-          <t>福建省-泉州市</t>
+          <t>河南省-平顶山市</t>
         </is>
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t>本次发行金额3亿元,用于直接投资或基金出资置换,对科技型企业提供股性资金支持,及偿还发行人本部有息债务。</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[25平发D2]</t>
         </is>
       </c>
       <c r="AC76" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,兴业银行股份有限公司,厦门银行股份有限公司,浙商银行股份有限公司,中信银行股份有限公司</t>
+          <t>国联民生证券承销保荐有限公司,华创证券有限责任公司</t>
         </is>
       </c>
       <c r="AD76" s="3"/>
       <c r="AE76" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF76" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG76" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>福建七匹狼集团有限公司2026年度第一期科技创新债券</t>
+          <t>平顶山发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种二)</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ76" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2033-08-31</t>
         </is>
       </c>
       <c r="AK76" s="3"/>
       <c r="AL76" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM76" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN76" s="3" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AM76" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN76" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP76" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP76" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ76" s="3" t="inlineStr">
         <is>
-          <t>轻工制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>纺织服饰</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
         <is>
-          <t>纺织服饰</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT76" s="3" t="inlineStr">
         <is>
-          <t>服装家纺</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU76" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-27.xlsx
+++ b/data/credit_bond_all_2026-08-27.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-01" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-02" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-01</t>
+          <t>数据来源：DM    2026-09-02</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>C 25.59</t>
+          <t>C 25.87</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>B- 46.97</t>
+          <t>B- 42.75</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B- 36.85</t>
+          <t>C 28.45</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.18</t>
+          <t>C+ 32.99</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>A- 60.53</t>
+          <t>A- 60.59</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.36</t>
+          <t>C+ 33.41</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B- 44.75</t>
+          <t>B- 43.88</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>A- 60.53</t>
+          <t>A- 60.59</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3539,7 +3539,7 @@
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.87</t>
+          <t>C+ 33.28</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 43.23</t>
+          <t>B- 43.42</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C 25.75</t>
+          <t>C 25.13</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4315,7 +4315,7 @@
       <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM18" s="3" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 10.16</t>
+          <t>C- 12.15</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C 25.91</t>
+          <t>C- 22.70</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -5005,7 +5005,7 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM21" s="3" t="inlineStr">
@@ -5475,7 +5475,7 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
@@ -5569,7 +5569,9 @@
       <c r="E24" s="4" t="n">
         <v>4.0</v>
       </c>
-      <c r="F24" s="3"/>
+      <c r="F24" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
           <t>1.80 ~ 2.80</t>
@@ -5611,7 +5613,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B+ 56.43</t>
+          <t>B+ 56.34</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5634,7 +5636,9 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="U24" s="3"/>
+      <c r="U24" s="4" t="n">
+        <v>1.05</v>
+      </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
@@ -5839,7 +5843,7 @@
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>A- 61.96</t>
+          <t>B+ 59.37</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -6065,7 +6069,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C- 22.59</t>
+          <t>C 25.81</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6293,7 +6297,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.42</t>
+          <t>D+ 8.02</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6523,7 +6527,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 13.70</t>
+          <t>C- 12.94</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6835,7 +6839,7 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -6973,7 +6977,7 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 37.31</t>
+          <t>B- 45.88</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7433,7 +7437,7 @@
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>D- 2.76</t>
+          <t>D 3.97</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -8125,7 +8129,7 @@
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>D 4.81</t>
+          <t>D+ 5.70</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8357,7 +8361,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 16.92</t>
+          <t>C- 17.29</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8453,7 +8457,7 @@
       </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8591,7 +8595,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.87</t>
+          <t>C+ 33.98</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8827,7 +8831,7 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.00</t>
+          <t>B- 39.11</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -9281,7 +9285,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C- 15.45</t>
+          <t>C 28.33</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9446,72 +9450,72 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26淮安交通MTN003</t>
+          <t>26太新Y7</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>102683421.IB</t>
+          <t>245995.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>7+N</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>4.6</v>
+        <v>9.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>4.6</v>
+        <v>9.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.40</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26淮安交通MTN002</t>
+          <t>26太新Y6</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>1.80Y</t>
+          <t>6.98Y+N</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1.6752</t>
+          <t>2.2233</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>1.7000/--</t>
+          <t>--/2.2150</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>淮安市交通控股集团有限公司</t>
+          <t>无锡市太湖新城发展集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>C- 18.60</t>
+          <t>B- 35.06</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9521,7 +9525,7 @@
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
@@ -9531,50 +9535,48 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>4.0217</v>
-      </c>
-      <c r="V41" s="4" t="n">
-        <v>1.5</v>
-      </c>
+        <v>2.19</v>
+      </c>
+      <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>2.37%~2.47%</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行金额4.6亿元,根据发行人的资金需求,拟全部用于偿还发行人债务融资工具本金[26淮安交通CP002]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券的本金[24太新Y1]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,杭州银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信证券股份有限公司,国联民生证券承销保荐有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
       <c r="AE41" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF41" s="3" t="inlineStr">
@@ -9584,12 +9586,12 @@
       </c>
       <c r="AG41" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>淮安市交通控股集团有限公司2026年度第三期中期票据</t>
+          <t>无锡市太湖新城发展集团有限公司2026年面向专业投资者公开发行可续期公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
@@ -9599,13 +9601,13 @@
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2033-09-01</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AM41" s="3" t="inlineStr">
@@ -9615,17 +9617,17 @@
       </c>
       <c r="AN41" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP41" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ41" s="3" t="inlineStr">
@@ -9635,12 +9637,12 @@
       </c>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT41" s="3" t="inlineStr">
@@ -9660,7 +9662,7 @@
       </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX41" s="3" t="inlineStr">
@@ -9678,17 +9680,17 @@
     <row r="42" customHeight="true" ht="18.0">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26万盛01</t>
+          <t>26淮安交通MTN003</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>08-27 19:00</t>
+          <t>08-27 18:00</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>283784.SH</t>
+          <t>102683421.IB</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
@@ -9697,53 +9699,53 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>6.0</v>
+        <v>4.6</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>6.0</v>
+        <v>4.6</v>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.70 ~ 2.40</t>
         </is>
       </c>
       <c r="H42" s="4" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>25万盛04</t>
+          <t>26淮安交通MTN002</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>4.29Y</t>
+          <t>1.80Y</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>2.3229</t>
+          <t>1.6752</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.7000/--</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>重庆市万盛经济技术开发区开发投资集团有限公司</t>
+          <t>淮安市交通控股集团有限公司</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t>B- 41.82</t>
+          <t>C- 20.14</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
@@ -9753,7 +9755,7 @@
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
@@ -9767,44 +9769,46 @@
         </is>
       </c>
       <c r="U42" s="4" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="V42" s="3"/>
+        <v>4.0217</v>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>2.46%~2.56%</t>
+          <t>1.73%~1.83%</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z42" s="3"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
-          <t>重庆市-重庆市万盛经济技术开发区</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB42" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟发行规模为不超过6.00亿元(含6.00亿元)，募集资金扣除发行费用后，拟用于偿还公司到期的公司债券本金[24万盛01,23万盛05]</t>
+          <t>本期中期票据发行金额4.6亿元,根据发行人的资金需求,拟全部用于偿还发行人债务融资工具本金[26淮安交通CP002]</t>
         </is>
       </c>
       <c r="AC42" s="3" t="inlineStr">
         <is>
-          <t>华源证券股份有限公司</t>
+          <t>中信银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF42" s="3" t="inlineStr">
@@ -9814,17 +9818,17 @@
       </c>
       <c r="AG42" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH42" s="3" t="inlineStr">
         <is>
-          <t>重庆市万盛经济技术开发区开发投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>淮安市交通控股集团有限公司2026年度第三期中期票据</t>
         </is>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ42" s="3" t="inlineStr">
@@ -9835,7 +9839,7 @@
       <c r="AK42" s="3"/>
       <c r="AL42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM42" s="3" t="inlineStr">
@@ -9850,12 +9854,12 @@
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP42" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ42" s="3" t="inlineStr">
@@ -9865,12 +9869,12 @@
       </c>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT42" s="3" t="inlineStr">
@@ -9908,53 +9912,57 @@
     <row r="43" customHeight="true" ht="18.0">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN001(资产担保)(取消发行)</t>
+          <t>26万盛01</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>DY102683428.IB</t>
+          <t>283784.SH</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="F43" s="3"/>
+        <v>6.0</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>6.0</v>
+      </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.79</t>
-        </is>
-      </c>
-      <c r="H43" s="3"/>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>2.35</v>
+      </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>26温州交运MTN002</t>
+          <t>25万盛04</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2.87Y</t>
+          <t>4.29Y</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>1.7766</t>
+          <t>2.3229</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -9964,12 +9972,12 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司</t>
+          <t>重庆市万盛经济技术开发区开发投资集团有限公司</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t>C- 18.13</t>
+          <t>B- 40.86</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
@@ -9979,7 +9987,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -9992,14 +10000,20 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U43" s="3"/>
+      <c r="U43" s="4" t="n">
+        <v>4.15</v>
+      </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X43" s="3"/>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>2.46%~2.56%</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
           <t>AA</t>
@@ -10008,27 +10022,23 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
-          <t>浙江省-温州市</t>
+          <t>重庆市-重庆市万盛经济技术开发区</t>
         </is>
       </c>
       <c r="AB43" s="3" t="inlineStr">
         <is>
-          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币,用于偿还金融机构借款</t>
+          <t>本期债券拟发行规模为不超过6.00亿元(含6.00亿元)，募集资金扣除发行费用后，拟用于偿还公司到期的公司债券本金[24万盛01,23万盛05]</t>
         </is>
       </c>
       <c r="AC43" s="3" t="inlineStr">
         <is>
-          <t>浙商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD43" s="3" t="inlineStr">
-        <is>
-          <t>温州交运集团房地产投资开发有限公司</t>
-        </is>
-      </c>
+          <t>华源证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF43" s="3" t="inlineStr">
@@ -10038,28 +10048,28 @@
       </c>
       <c r="AG43" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH43" s="3" t="inlineStr">
         <is>
-          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具(取消发行)</t>
+          <t>重庆市万盛经济技术开发区开发投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI43" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ43" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM43" s="3" t="inlineStr">
@@ -10074,7 +10084,7 @@
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP43" s="3" t="inlineStr">
@@ -10084,22 +10094,22 @@
       </c>
       <c r="AQ43" s="3" t="inlineStr">
         <is>
-          <t>交通运输</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
         <is>
-          <t>非盈利性交运服务</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT43" s="3" t="inlineStr">
         <is>
-          <t>公交</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU43" s="3" t="inlineStr">
@@ -10109,7 +10119,7 @@
       </c>
       <c r="AV43" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW43" s="3" t="inlineStr">
@@ -10132,70 +10142,68 @@
     <row r="44" customHeight="true" ht="18.0">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>26太新Y7</t>
+          <t>26温州交运MTN001(资产担保)(取消发行)</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>08-27 19:00</t>
+          <t>08-27 18:00</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>245995.SH</t>
+          <t>DY102683428.IB</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>7+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>9.0</v>
+        <v>1.0</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>2.25</v>
-      </c>
+          <t>1.50 ~ 1.79</t>
+        </is>
+      </c>
+      <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>26太新Y6</t>
+          <t>26温州交运MTN002</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>6.98Y+N</t>
+          <t>2.87Y</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2.2233</t>
+          <t>1.7766</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t>--/2.2150</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>温州市交通运输集团有限公司</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t>B- 40.72</t>
+          <t>C- 18.84</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
@@ -10205,7 +10213,7 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -10215,46 +10223,46 @@
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U44" s="3"/>
       <c r="V44" s="3"/>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t>2.37%~2.47%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X44" s="3"/>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z44" s="3"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>浙江省-温州市</t>
         </is>
       </c>
       <c r="AB44" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券的本金[24太新Y1]</t>
+          <t>本期资产担保债务融资工具拟发行金额为1亿元人民币,用于偿还金融机构借款</t>
         </is>
       </c>
       <c r="AC44" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信证券股份有限公司,国联民生证券承销保荐有限公司,东吴证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD44" s="3"/>
+          <t>浙商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr">
+        <is>
+          <t>温州交运集团房地产投资开发有限公司</t>
+        </is>
+      </c>
       <c r="AE44" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF44" s="3" t="inlineStr">
@@ -10264,12 +10272,12 @@
       </c>
       <c r="AG44" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH44" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年面向专业投资者公开发行可续期公司债券(第四期)</t>
+          <t>温州市交通运输集团有限公司2026年度第一期资产担保债务融资工具(取消发行)</t>
         </is>
       </c>
       <c r="AI44" s="3" t="inlineStr">
@@ -10279,68 +10287,68 @@
       </c>
       <c r="AJ44" s="3" t="inlineStr">
         <is>
-          <t>2033-09-01</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ44" s="3" t="inlineStr">
+        <is>
+          <t>交通运输</t>
+        </is>
+      </c>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>非盈利性交运服务</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>公交</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM44" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO44" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP44" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ44" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR44" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS44" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT44" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU44" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV44" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW44" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX44" s="3" t="inlineStr">
@@ -10423,7 +10431,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.46</t>
+          <t>B- 36.44</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -10661,7 +10669,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t>B- 40.14</t>
+          <t>B- 42.69</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
@@ -10893,7 +10901,7 @@
       </c>
       <c r="P47" s="3" t="inlineStr">
         <is>
-          <t>B- 40.05</t>
+          <t>B- 39.84</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
@@ -11357,7 +11365,7 @@
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
-          <t>C- 13.70</t>
+          <t>C- 12.94</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
@@ -11587,7 +11595,7 @@
       </c>
       <c r="P50" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.95</t>
+          <t>D+ 6.45</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
@@ -11817,7 +11825,7 @@
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
-          <t>C- 23.89</t>
+          <t>C- 24.30</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
@@ -12045,7 +12053,7 @@
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
-          <t>B- 40.00</t>
+          <t>B- 44.98</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
@@ -12273,7 +12281,7 @@
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
-          <t>B- 40.00</t>
+          <t>B- 44.98</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
@@ -12503,7 +12511,7 @@
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
-          <t>A 73.22</t>
+          <t>A 76.08</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
@@ -12965,7 +12973,7 @@
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
-          <t>C- 17.67</t>
+          <t>C- 20.32</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
@@ -13199,7 +13207,7 @@
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
-          <t>C- 21.04</t>
+          <t>C- 20.87</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
@@ -13665,7 +13673,7 @@
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
-          <t>C- 12.72</t>
+          <t>C- 15.15</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
@@ -13895,7 +13903,7 @@
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
-          <t>C- 20.00</t>
+          <t>B- 45.00</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
@@ -14121,7 +14129,7 @@
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.47</t>
+          <t>C 27.11</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
@@ -14359,7 +14367,7 @@
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
-          <t>C- 17.91</t>
+          <t>C- 12.46</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
@@ -14823,7 +14831,7 @@
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.21</t>
+          <t>D+ 8.67</t>
         </is>
       </c>
       <c r="Q64" s="3" t="inlineStr">
@@ -15057,7 +15065,7 @@
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.72</t>
+          <t>C+ 32.53</t>
         </is>
       </c>
       <c r="Q65" s="3" t="inlineStr">
@@ -15291,7 +15299,7 @@
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.72</t>
+          <t>C+ 32.53</t>
         </is>
       </c>
       <c r="Q66" s="3" t="inlineStr">
@@ -15757,7 +15765,7 @@
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.87</t>
+          <t>C+ 33.98</t>
         </is>
       </c>
       <c r="Q68" s="3" t="inlineStr">
@@ -15989,7 +15997,7 @@
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
-          <t>C 26.08</t>
+          <t>C 28.02</t>
         </is>
       </c>
       <c r="Q69" s="3" t="inlineStr">
@@ -16225,7 +16233,7 @@
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
-          <t>C- 17.46</t>
+          <t>C- 18.39</t>
         </is>
       </c>
       <c r="Q70" s="3" t="inlineStr">
@@ -16455,7 +16463,7 @@
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
-          <t>B- 45.77</t>
+          <t>B- 47.31</t>
         </is>
       </c>
       <c r="Q71" s="3" t="inlineStr">
@@ -16915,7 +16923,7 @@
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
-          <t>C- 22.59</t>
+          <t>C 25.81</t>
         </is>
       </c>
       <c r="Q73" s="3" t="inlineStr">
@@ -17003,7 +17011,7 @@
       <c r="AK73" s="3"/>
       <c r="AL73" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM73" s="3" t="inlineStr">
@@ -17231,7 +17239,7 @@
       <c r="AK74" s="3"/>
       <c r="AL74" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM74" s="3" t="inlineStr">
@@ -17603,7 +17611,7 @@
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>B 54.58</t>
+          <t>A- 67.73</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-08-27.xlsx
+++ b/data/credit_bond_all_2026-08-27.xlsx
@@ -3167,7 +3167,7 @@
       <c r="AK13" s="3"/>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -4162,7 +4162,7 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26新乡Y1</t>
+          <t>26临开Y1</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -4172,47 +4172,47 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>283836.SH</t>
+          <t>283847.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+N</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.80 ~ 2.60</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26新乡投资PPN002</t>
+          <t>25临开Y1</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>1.65Y+N</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.8637</t>
+          <t>1.8062</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>新乡投资集团有限公司</t>
+          <t>杭州临平开发投资集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C 25.13</t>
+          <t>C- 12.15</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4247,38 +4247,38 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.5</v>
+        <v>2.7533</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X18" s="3"/>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>河南省-新乡市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还即将到期公司债券本金。[23 新乡03]</t>
+          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还公司债券本金。[23临开Y1]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国联民生证券承销保荐有限公司</t>
+          <t>国金证券股份有限公司,中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>新乡投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
+          <t>杭州临平开发投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4309,13 +4309,13 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM18" s="3" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="AN18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="AX18" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY18" s="3" t="inlineStr">
@@ -4388,7 +4388,7 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26临开Y1</t>
+          <t>26上金02</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -4398,62 +4398,62 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>283847.SH</t>
+          <t>245969.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.60</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>25临开Y1</t>
+          <t>26上金01</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.65Y+N</t>
+          <t>2.60Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.8062</t>
+          <t>1.6812</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.6900</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>杭州临平开发投资集团有限公司</t>
+          <t>上海汽车集团金控管理有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 12.15</t>
+          <t>C+ 33.15</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4473,38 +4473,42 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.7533</v>
+        <v>3.3188</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X19" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>1.73%~1.83%</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>上海市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,全部用于偿还公司债券本金。[23临开Y1]</t>
+          <t>本期公司债券募集资金拟用于偿还到期公司债券[23上金K2]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>国金证券股份有限公司,中国国际金融股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信证券股份有限公司,平安证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
@@ -4525,23 +4529,27 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>杭州临平开发投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
+          <t>上海汽车集团金控管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
-        </is>
-      </c>
-      <c r="AK19" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t/>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4551,37 +4559,37 @@
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4596,7 +4604,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
@@ -4614,7 +4622,7 @@
     <row r="20" customHeight="true" ht="18.0">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>26上金02</t>
+          <t>26金城02</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -4624,19 +4632,19 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>245969.SH</t>
+          <t>283812.SH</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>16.0</v>
+        <v>5.0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>16.0</v>
+        <v>5.0</v>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
@@ -4644,42 +4652,42 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>26上金01</t>
+          <t>26金城01</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2.60Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>1.6812</t>
+          <t>1.7269</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>--/1.6900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>上海汽车集团金控管理有限公司</t>
+          <t>张家港市金城投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.15</t>
+          <t>C- 22.70</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -4703,38 +4711,38 @@
         </is>
       </c>
       <c r="U20" s="4" t="n">
-        <v>3.3188</v>
+        <v>5.87</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t>1.73%~1.83%</t>
+          <t>1.80%~1.90%</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z20" s="3"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB20" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金拟用于偿还到期公司债券[23上金K2]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[23 金城04]</t>
         </is>
       </c>
       <c r="AC20" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信证券股份有限公司,平安证券股份有限公司</t>
+          <t>东吴证券股份有限公司,国金证券股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD20" s="3"/>
@@ -4755,27 +4763,23 @@
       </c>
       <c r="AH20" s="3" t="inlineStr">
         <is>
-          <t>上海汽车集团金控管理有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>张家港市金城投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ20" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK20" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK20" s="3"/>
       <c r="AL20" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM20" s="3" t="inlineStr">
@@ -4790,12 +4794,12 @@
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP20" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ20" s="3" t="inlineStr">
@@ -4805,17 +4809,17 @@
       </c>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr">
@@ -4848,7 +4852,7 @@
     <row r="21" customHeight="true" ht="18.0">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>26金城02</t>
+          <t>26蚌水02(取消发行)</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -4858,47 +4862,43 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>283812.SH</t>
+          <t>DY283758.SH</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="F21" s="3"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>1.77</v>
-      </c>
+          <t>1.90 ~ 2.90</t>
+        </is>
+      </c>
+      <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>26金城01</t>
+          <t>25邕振V1</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>3.67Y+5.00Y</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>1.7269</t>
+          <t>2.0953</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>张家港市金城投资发展集团有限公司</t>
+          <t>蚌埠靓淮河水利投资集团有限公司</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t>C- 22.70</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
@@ -4933,45 +4933,51 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="n">
-        <v>5.87</v>
-      </c>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t>1.80%~1.90%</t>
+          <t>2.20%~2.30%</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
           <t>AA+</t>
         </is>
       </c>
-      <c r="Z21" s="3"/>
       <c r="AA21" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>安徽省-蚌埠市</t>
         </is>
       </c>
       <c r="AB21" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券本金[23 金城04]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将5亿元用于偿还到期公司债本金[23蚌水01]</t>
         </is>
       </c>
       <c r="AC21" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司,国金证券股份有限公司,国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD21" s="3"/>
+          <t>招商证券股份有限公司,中信证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr">
+        <is>
+          <t>蚌埠市国有资本运营控股集团有限公司</t>
+        </is>
+      </c>
       <c r="AE21" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -4989,7 +4995,7 @@
       </c>
       <c r="AH21" s="3" t="inlineStr">
         <is>
-          <t>张家港市金城投资发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>蚌埠靓淮河水利投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)(取消发行)</t>
         </is>
       </c>
       <c r="AI21" s="3" t="inlineStr">
@@ -4999,13 +5005,13 @@
       </c>
       <c r="AJ21" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AM21" s="3" t="inlineStr">
@@ -5015,7 +5021,7 @@
       </c>
       <c r="AN21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO21" s="3" t="inlineStr">
@@ -5025,22 +5031,22 @@
       </c>
       <c r="AP21" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ21" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
@@ -5055,7 +5061,7 @@
       </c>
       <c r="AV21" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW21" s="3" t="inlineStr">
@@ -5078,7 +5084,7 @@
     <row r="22" customHeight="true" ht="18.0">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>26蚌水02(取消发行)</t>
+          <t>26蚌水01</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -5088,28 +5094,32 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>DY283758.SH</t>
+          <t>283752.SH</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
         <v>2.5</v>
       </c>
-      <c r="F22" s="3"/>
+      <c r="F22" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.90</t>
-        </is>
-      </c>
-      <c r="H22" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>1.9</v>
+      </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
@@ -5162,7 +5172,9 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U22" s="3"/>
+      <c r="U22" s="4" t="n">
+        <v>5.6</v>
+      </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3" t="inlineStr">
         <is>
@@ -5171,7 +5183,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t>2.20%~2.30%</t>
+          <t>2.08%~2.18%</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
@@ -5221,7 +5233,7 @@
       </c>
       <c r="AH22" s="3" t="inlineStr">
         <is>
-          <t>蚌埠靓淮河水利投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种二)(取消发行)</t>
+          <t>蚌埠靓淮河水利投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
         </is>
       </c>
       <c r="AI22" s="3" t="inlineStr">
@@ -5231,13 +5243,13 @@
       </c>
       <c r="AJ22" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM22" s="3" t="inlineStr">
@@ -5310,7 +5322,7 @@
     <row r="23" customHeight="true" ht="18.0">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>26蚌水01</t>
+          <t>26京城01</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -5320,7 +5332,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>283752.SH</t>
+          <t>283799.SH</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -5329,119 +5341,107 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.5</v>
+        <v>4.0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.9</v>
+        <v>2.33</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>25京城01</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>1.79Y</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>1.9331</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>--/1.8800</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>北京城建投资发展股份有限公司</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>B+ 56.34</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>08-27 16:00</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>25邕振V1</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>3.67Y+5.00Y</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t>2.0953</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>蚌埠靓淮河水利投资集团有限公司</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="R23" s="3" t="inlineStr">
-        <is>
-          <t>08-27 15:00</t>
-        </is>
-      </c>
-      <c r="S23" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U23" s="4" t="n">
-        <v>5.6</v>
+        <v>1.05</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X23" s="3" t="inlineStr">
-        <is>
-          <t>2.08%~2.18%</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X23" s="3"/>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
-        </is>
-      </c>
-      <c r="Z23" s="3" t="inlineStr">
-        <is>
-          <t>AA+</t>
-        </is>
-      </c>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z23" s="3"/>
       <c r="AA23" s="3" t="inlineStr">
         <is>
-          <t>安徽省-蚌埠市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB23" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将5亿元用于偿还到期公司债本金[23蚌水01]</t>
+          <t>本期债券募集资金4亿元拟全部用于偿还公司债券本金[24北城01]</t>
         </is>
       </c>
       <c r="AC23" s="3" t="inlineStr">
         <is>
-          <t>招商证券股份有限公司,中信证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD23" s="3" t="inlineStr">
-        <is>
-          <t>蚌埠市国有资本运营控股集团有限公司</t>
-        </is>
-      </c>
+          <t>中信建投证券股份有限公司,中信证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+        </is>
+      </c>
+      <c r="AD23" s="3"/>
       <c r="AE23" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -5459,7 +5459,7 @@
       </c>
       <c r="AH23" s="3" t="inlineStr">
         <is>
-          <t>蚌埠靓淮河水利投资集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)(品种一)</t>
+          <t>北京城建投资发展股份有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI23" s="3" t="inlineStr">
@@ -5469,13 +5469,17 @@
       </c>
       <c r="AJ23" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
-        </is>
-      </c>
-      <c r="AK23" s="3"/>
+          <t>2029-09-01</t>
+        </is>
+      </c>
+      <c r="AK23" s="3" t="inlineStr">
+        <is>
+          <t>休2</t>
+        </is>
+      </c>
       <c r="AL23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AM23" s="3" t="inlineStr">
@@ -5485,37 +5489,37 @@
       </c>
       <c r="AN23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP23" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AQ23" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>房地产</t>
         </is>
       </c>
       <c r="AR23" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>综合地产开发</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房地产开发</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr">
@@ -5525,7 +5529,7 @@
       </c>
       <c r="AV23" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW23" s="3" t="inlineStr">
@@ -5548,7 +5552,7 @@
     <row r="24" customHeight="true" ht="18.0">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>26京城01</t>
+          <t>26国新01</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -5558,62 +5562,62 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>283799.SH</t>
+          <t>245985.SH</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4.0</v>
+        <v>20.0</v>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.20 ~ 2.20</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>2.33</v>
+        <v>1.72</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>25京城01</t>
+          <t>21国新控股MTN002</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>1.79Y</t>
+          <t>4.95Y</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>1.9331</t>
+          <t>1.7413</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>--/1.8800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>北京城建投资发展股份有限公司</t>
+          <t>中国国新控股有限责任公司</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t>B+ 56.34</t>
+          <t>B+ 59.37</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
@@ -5623,7 +5627,7 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>08-27 16:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
@@ -5633,19 +5637,23 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.05</v>
+        <v>3.28</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X24" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>1.69%~1.79%</t>
+        </is>
+      </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -5659,12 +5667,12 @@
       </c>
       <c r="AB24" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金4亿元拟全部用于偿还公司债券本金[24北城01]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于生产性支出,包括但不限于补充流动资金、偿还有息债务等符合法律法规及监管要求的用途</t>
         </is>
       </c>
       <c r="AC24" s="3" t="inlineStr">
         <is>
-          <t>中信建投证券股份有限公司,中信证券股份有限公司,第一创业证券承销保荐有限责任公司</t>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,国新证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD24" s="3"/>
@@ -5675,7 +5683,7 @@
       </c>
       <c r="AF24" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG24" s="3" t="inlineStr">
@@ -5685,27 +5693,23 @@
       </c>
       <c r="AH24" s="3" t="inlineStr">
         <is>
-          <t>北京城建投资发展股份有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>中国国新控股有限责任公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI24" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ24" s="3" t="inlineStr">
         <is>
-          <t>2029-09-01</t>
-        </is>
-      </c>
-      <c r="AK24" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-08-28</t>
+        </is>
+      </c>
+      <c r="AK24" s="3"/>
       <c r="AL24" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM24" s="3" t="inlineStr">
@@ -5715,7 +5719,7 @@
       </c>
       <c r="AN24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO24" s="3" t="inlineStr">
@@ -5725,27 +5729,27 @@
       </c>
       <c r="AP24" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ24" s="3" t="inlineStr">
         <is>
-          <t>房地产</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>综合地产开发</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>房地产开发</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr">
@@ -5778,7 +5782,7 @@
     <row r="25" customHeight="true" ht="18.0">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>26国新01</t>
+          <t>26平发02(取消发行)</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -5788,7 +5792,7 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>245985.SH</t>
+          <t>DY283855.SH</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
@@ -5797,38 +5801,34 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>20.0</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>20.0</v>
-      </c>
+        <v>4.0</v>
+      </c>
+      <c r="F25" s="3"/>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>1.72</v>
-      </c>
+          <t>2.00 ~ 2.60</t>
+        </is>
+      </c>
+      <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>21国新控股MTN002</t>
+          <t>26平发01</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>4.95Y</t>
+          <t>4.41Y</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>1.7413</t>
+          <t>2.0994</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -5838,12 +5838,12 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>中国国新控股有限责任公司</t>
+          <t>平顶山发展投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t>B+ 59.37</t>
+          <t>C 25.81</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
@@ -5863,42 +5863,36 @@
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="n">
-        <v>3.28</v>
-      </c>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t>1.69%~1.79%</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X25" s="3"/>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z25" s="3"/>
       <c r="AA25" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>河南省-平顶山市</t>
         </is>
       </c>
       <c r="AB25" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于生产性支出,包括但不限于补充流动资金、偿还有息债务等符合法律法规及监管要求的用途</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[25平发D2]</t>
         </is>
       </c>
       <c r="AC25" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司,国新证券股份有限公司,光大证券股份有限公司,招商证券股份有限公司</t>
+          <t>国联民生证券承销保荐有限公司,华创证券有限责任公司</t>
         </is>
       </c>
       <c r="AD25" s="3"/>
@@ -5909,7 +5903,7 @@
       </c>
       <c r="AF25" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG25" s="3" t="inlineStr">
@@ -5919,23 +5913,27 @@
       </c>
       <c r="AH25" s="3" t="inlineStr">
         <is>
-          <t>中国国新控股有限责任公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>平顶山发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI25" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ25" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
-        </is>
-      </c>
-      <c r="AK25" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t/>
         </is>
       </c>
       <c r="AM25" s="3" t="inlineStr">
@@ -5945,17 +5943,17 @@
       </c>
       <c r="AN25" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP25" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ25" s="3" t="inlineStr">
@@ -5965,17 +5963,17 @@
       </c>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>产业控股</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr">
@@ -6008,53 +6006,57 @@
     <row r="26" customHeight="true" ht="18.0">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>26平发02(取消发行)</t>
+          <t>26青岛黄岛MTN001</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>08-27 19:00</t>
+          <t>08-27 18:00</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>DY283855.SH</t>
+          <t>102683441.IB</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F26" s="3"/>
+        <v>4.78</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>4.78</v>
+      </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 2.60</t>
-        </is>
-      </c>
-      <c r="H26" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>1.93</v>
+      </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>26平发01</t>
+          <t>24青岛黄岛MTN004B</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>4.41Y</t>
+          <t>3.01Y</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>2.0994</t>
+          <t>1.9262</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -6064,12 +6066,12 @@
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>平顶山发展投资控股集团有限公司</t>
+          <t>青岛黄岛发展(集团)有限公司</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t>C 25.81</t>
+          <t>D+ 8.02</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
@@ -6079,7 +6081,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 10:00</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
@@ -6089,17 +6091,25 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="n">
+        <v>3.0126</v>
+      </c>
+      <c r="V26" s="4" t="n">
+        <v>1.45</v>
+      </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="X26" s="3"/>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>1.89%~1.99%</t>
+        </is>
+      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -6108,23 +6118,23 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3" t="inlineStr">
         <is>
-          <t>河南省-平顶山市</t>
+          <t>山东省-青岛市</t>
         </is>
       </c>
       <c r="AB26" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期的公司债券本金。[25平发D2]</t>
+          <t>本期中期票据募集资金全部用于偿还发行人存量债务融资工具[24青岛黄岛PPN003]</t>
         </is>
       </c>
       <c r="AC26" s="3" t="inlineStr">
         <is>
-          <t>国联民生证券承销保荐有限公司,华创证券有限责任公司</t>
+          <t>兴业银行股份有限公司,浙商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD26" s="3"/>
       <c r="AE26" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF26" s="3" t="inlineStr">
@@ -6134,79 +6144,75 @@
       </c>
       <c r="AG26" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH26" s="3" t="inlineStr">
         <is>
-          <t>平顶山发展投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)(品种一)(取消发行)</t>
+          <t>青岛黄岛发展(集团)有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI26" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ26" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK26" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-28</t>
+        </is>
+      </c>
+      <c r="AK26" s="3"/>
       <c r="AL26" s="3" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>贸易</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AO26" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ26" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR26" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS26" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV26" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -6227,12 +6233,14 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ26" s="3"/>
+      <c r="AZ26" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="27" customHeight="true" ht="18.0">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>26青岛黄岛MTN001</t>
+          <t>26柳州东投MTN001A(取消发行)</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -6242,47 +6250,43 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>102683441.IB</t>
+          <t>DY102683439.IB</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>2+2+1</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>4.78</v>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="3"/>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>1.93</v>
-      </c>
+          <t>1.20 ~ 2.20</t>
+        </is>
+      </c>
+      <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>24青岛黄岛MTN004B</t>
+          <t>25柳州东投MTN002</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>3.01Y</t>
+          <t>2.00Y+2.00Y</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>1.9262</t>
+          <t>1.9959</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -6292,12 +6296,12 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>青岛黄岛发展(集团)有限公司</t>
+          <t>广西柳州市东城投资开发集团有限公司</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.02</t>
+          <t>C- 12.94</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
@@ -6307,7 +6311,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>08-27 10:00</t>
+          <t>08-27 14:00</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
@@ -6320,20 +6324,16 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U27" s="4" t="n">
-        <v>3.0126</v>
-      </c>
-      <c r="V27" s="4" t="n">
-        <v>1.45</v>
-      </c>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t>1.89%~1.99%</t>
+          <t>2.00%~2.10%</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
@@ -6344,17 +6344,17 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3" t="inlineStr">
         <is>
-          <t>山东省-青岛市</t>
+          <t>广西壮族自治区-柳州市</t>
         </is>
       </c>
       <c r="AB27" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据募集资金全部用于偿还发行人存量债务融资工具[24青岛黄岛PPN003]</t>
+          <t>公司发行本期中期票据规模不超过3亿元,用于优化债务结构,所偿还债务均不属于政府隐性债务。[23柳州东投MTN001]</t>
         </is>
       </c>
       <c r="AC27" s="3" t="inlineStr">
         <is>
-          <t>兴业银行股份有限公司,浙商银行股份有限公司</t>
+          <t>东方证券股份有限公司,广西北部湾银行股份有限公司</t>
         </is>
       </c>
       <c r="AD27" s="3"/>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="AH27" s="3" t="inlineStr">
         <is>
-          <t>青岛黄岛发展(集团)有限公司2026年度第一期中期票据</t>
+          <t>广西柳州市东城投资开发集团有限公司2026年度第一期中期票据(品种一)(取消发行)</t>
         </is>
       </c>
       <c r="AI27" s="3" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="AJ27" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK27" s="3"/>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="AP27" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ27" s="3" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="AW27" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX27" s="3" t="inlineStr">
@@ -6459,60 +6459,54 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="AZ27" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ27" s="3"/>
     </row>
     <row r="28" customHeight="true" ht="18.0">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>26柳州东投MTN001A(取消发行)</t>
+          <t>26泗洪01</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>DY102683439.IB</t>
+          <t>283814.SH</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>2+2+1</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F28" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>1.20 ~ 2.20</t>
-        </is>
-      </c>
-      <c r="H28" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>1.97</v>
+      </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>25柳州东投MTN002</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>2.00Y+2.00Y</t>
-        </is>
-      </c>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="K28" s="3"/>
+      <c r="L28" s="3"/>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1.9959</t>
+          <t>--</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -6522,12 +6516,12 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>广西柳州市东城投资开发集团有限公司</t>
+          <t>泗洪县宏源公有资产经营集团有限公司</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>C- 12.94</t>
+          <t>D- 1.23</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -6537,7 +6531,7 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>08-27 14:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
@@ -6550,43 +6544,45 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="U28" s="3"/>
+      <c r="U28" s="4" t="n">
+        <v>2.18</v>
+      </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t>2.00%~2.10%</t>
+          <t>1.94%~2.04%</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3" t="inlineStr">
         <is>
-          <t>广西壮族自治区-柳州市</t>
+          <t>江苏省-宿迁市</t>
         </is>
       </c>
       <c r="AB28" s="3" t="inlineStr">
         <is>
-          <t>公司发行本期中期票据规模不超过3亿元,用于优化债务结构,所偿还债务均不属于政府隐性债务。[23柳州东投MTN001]</t>
+          <t>本期公司债券发行总额不超过人民币10亿元(含10亿元),发行人在扣除发行费用后,全部用于偿还回售的公司债券本金[23泗洪01]</t>
         </is>
       </c>
       <c r="AC28" s="3" t="inlineStr">
         <is>
-          <t>东方证券股份有限公司,广西北部湾银行股份有限公司</t>
+          <t>中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD28" s="3"/>
       <c r="AE28" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF28" s="3" t="inlineStr">
@@ -6596,17 +6592,17 @@
       </c>
       <c r="AG28" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH28" s="3" t="inlineStr">
         <is>
-          <t>广西柳州市东城投资开发集团有限公司2026年度第一期中期票据(品种一)(取消发行)</t>
+          <t>泗洪县宏源公有资产经营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI28" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ28" s="3" t="inlineStr">
@@ -6617,7 +6613,7 @@
       <c r="AK28" s="3"/>
       <c r="AL28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM28" s="3" t="inlineStr">
@@ -6632,12 +6628,12 @@
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP28" s="3" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ28" s="3" t="inlineStr">
@@ -6657,12 +6653,12 @@
       </c>
       <c r="AT28" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>房屋建设</t>
         </is>
       </c>
       <c r="AU28" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AV28" s="3" t="inlineStr">
@@ -6690,7 +6686,7 @@
     <row r="29" customHeight="true" ht="18.0">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>26泗洪01</t>
+          <t>26济运01</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -6700,109 +6696,117 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>283814.SH</t>
+          <t>283795.SH</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>10.0</v>
+        <v>0.23</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>10.0</v>
+        <v>0.23</v>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.00 ~ 3.20</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>1.97</v>
+        <v>2.75</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>24济运04</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>2.97Y</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>2.0553</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>2.0600/--</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>济宁市城运集团有限公司</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>B- 45.88</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>08-27 15:00</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>--/--</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>泗洪县宏源公有资产经营集团有限公司</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>D- 1.23</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>08-27 15:00</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
       <c r="U29" s="4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7-</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>1.94%~2.04%</t>
+          <t>2.09%~2.19%</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z29" s="3"/>
       <c r="AA29" s="3" t="inlineStr">
         <is>
-          <t>江苏省-宿迁市</t>
+          <t>山东省-济宁市</t>
         </is>
       </c>
       <c r="AB29" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券发行总额不超过人民币10亿元(含10亿元),发行人在扣除发行费用后,全部用于偿还回售的公司债券本金[23泗洪01]</t>
+          <t>本期债券募集资金0.23亿元,扣除发行费用后拟用于偿还公司债券本金或置换偿还到期公司债券本金的自有资金[23任兴03,23任兴04,23任城04]</t>
         </is>
       </c>
       <c r="AC29" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
+          <t>国投证券股份有限公司,恒泰长财证券有限责任公司,长城证券股份有限公司,申港证券股份有限公司</t>
         </is>
       </c>
       <c r="AD29" s="3"/>
@@ -6823,7 +6827,7 @@
       </c>
       <c r="AH29" s="3" t="inlineStr">
         <is>
-          <t>泗洪县宏源公有资产经营集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>济宁市城运集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI29" s="3" t="inlineStr">
@@ -6839,7 +6843,7 @@
       <c r="AK29" s="3"/>
       <c r="AL29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AM29" s="3" t="inlineStr">
@@ -6854,7 +6858,7 @@
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP29" s="3" t="inlineStr">
@@ -6879,12 +6883,12 @@
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>房屋建设</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV29" s="3" t="inlineStr">
@@ -6894,7 +6898,7 @@
       </c>
       <c r="AW29" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX29" s="3" t="inlineStr">
@@ -6912,7 +6916,7 @@
     <row r="30" customHeight="true" ht="18.0">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>26济运01</t>
+          <t>26金东02</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -6922,62 +6926,62 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>283795.SH</t>
+          <t>283736.SH</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.23</v>
+        <v>7.75</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.23</v>
+        <v>7.75</v>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.20</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>24济运04</t>
+          <t>24金东城投PPN002</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>2.97Y</t>
+          <t>3.05Y</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>2.0553</t>
+          <t>1.8499</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>2.0600/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>济宁市城运集团有限公司</t>
+          <t>泰州市金东城市建设投资集团有限公司</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>B- 45.88</t>
+          <t>C- 14.71</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -7001,17 +7005,17 @@
         </is>
       </c>
       <c r="U30" s="4" t="n">
-        <v>2.17</v>
+        <v>2.99</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t>2.09%~2.19%</t>
+          <t>1.83%~1.93%</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
@@ -7022,17 +7026,17 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3" t="inlineStr">
         <is>
-          <t>山东省-济宁市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB30" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金0.23亿元,扣除发行费用后拟用于偿还公司债券本金或置换偿还到期公司债券本金的自有资金[23任兴03,23任兴04,23任城04]</t>
+          <t>本期债券募集资金扣除发行费用后,全部用于偿还公司债券本金[23金东03]</t>
         </is>
       </c>
       <c r="AC30" s="3" t="inlineStr">
         <is>
-          <t>国投证券股份有限公司,恒泰长财证券有限责任公司,长城证券股份有限公司,申港证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,平安证券股份有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD30" s="3"/>
@@ -7053,7 +7057,7 @@
       </c>
       <c r="AH30" s="3" t="inlineStr">
         <is>
-          <t>济宁市城运集团有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>泰州市金东城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI30" s="3" t="inlineStr">
@@ -7063,7 +7067,7 @@
       </c>
       <c r="AJ30" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK30" s="3"/>
@@ -7084,27 +7088,27 @@
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP30" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7*无效</t>
         </is>
       </c>
       <c r="AQ30" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT30" s="3" t="inlineStr">
@@ -7142,7 +7146,7 @@
     <row r="31" customHeight="true" ht="18.0">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>26金东02</t>
+          <t>26苏农01</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -7152,7 +7156,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>283736.SH</t>
+          <t>245964.SH</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -7161,10 +7165,10 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>7.75</v>
+        <v>7.0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7.75</v>
+        <v>7.0</v>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
@@ -7172,27 +7176,27 @@
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>24金东城投PPN002</t>
+          <t>25苏农02</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>3.05Y</t>
+          <t>2.24Y</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1.8499</t>
+          <t>1.6973</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -7202,12 +7206,12 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>泰州市金东城市建设投资集团有限公司</t>
+          <t>苏州市农业发展集团有限公司</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t>C- 14.71</t>
+          <t>D 3.97</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
@@ -7231,38 +7235,38 @@
         </is>
       </c>
       <c r="U31" s="4" t="n">
-        <v>2.99</v>
+        <v>3.37</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t>1.83%~1.93%</t>
+          <t>1.71%~1.81%</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>江苏省-苏州市</t>
         </is>
       </c>
       <c r="AB31" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,全部用于偿还公司债券本金[23金东03]</t>
+          <t>本期债券募集资金7.00亿元扣除发行费用后,4.00亿元用于偿还到期公司债券本金,剩余全部用于偿还其他有息负债。[21苏农02]</t>
         </is>
       </c>
       <c r="AC31" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,平安证券股份有限公司,东吴证券股份有限公司</t>
+          <t>东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD31" s="3"/>
@@ -7283,12 +7287,12 @@
       </c>
       <c r="AH31" s="3" t="inlineStr">
         <is>
-          <t>泰州市金东城市建设投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>苏州市农业发展集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI31" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ31" s="3" t="inlineStr">
@@ -7304,7 +7308,7 @@
       </c>
       <c r="AM31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AN31" s="3" t="inlineStr">
@@ -7314,12 +7318,12 @@
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP31" s="3" t="inlineStr">
         <is>
-          <t>7*无效</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ31" s="3" t="inlineStr">
@@ -7329,17 +7333,17 @@
       </c>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>产业控股</t>
         </is>
       </c>
       <c r="AT31" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU31" s="3" t="inlineStr">
@@ -7372,29 +7376,29 @@
     <row r="32" customHeight="true" ht="18.0">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>26苏农01</t>
+          <t>26东港投资PPN001</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>08-27 19:00</t>
+          <t>08-27 18:00</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>245964.SH</t>
+          <t>032680497.IB</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
@@ -7402,42 +7406,42 @@
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>25苏农02</t>
+          <t>26东港02</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2.24Y</t>
+          <t>2.96Y+2.00Y</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1.6973</t>
+          <t>1.8000</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.7300</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>苏州市农业发展集团有限公司</t>
+          <t>东港投资发展集团有限公司</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t>D 3.97</t>
+          <t>B- 37.72</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
@@ -7461,44 +7465,44 @@
         </is>
       </c>
       <c r="U32" s="4" t="n">
-        <v>3.37</v>
+        <v>2.8667</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z32" s="3"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
-          <t>江苏省-苏州市</t>
+          <t>浙江省-舟山市</t>
         </is>
       </c>
       <c r="AB32" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金7.00亿元扣除发行费用后,4.00亿元用于偿还到期公司债券本金,剩余全部用于偿还其他有息负债。[21苏农02]</t>
+          <t>发行人本期定向债务融资工具募集资金中,3.00亿元拟用于偿还21东港投资PPN001的本金[21东港投资PPN001]</t>
         </is>
       </c>
       <c r="AC32" s="3" t="inlineStr">
         <is>
-          <t>东吴证券股份有限公司</t>
+          <t>杭州银行股份有限公司,国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF32" s="3" t="inlineStr">
@@ -7508,33 +7512,33 @@
       </c>
       <c r="AG32" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH32" s="3" t="inlineStr">
         <is>
-          <t>苏州市农业发展集团有限公司2026年面向专业投资者公开发行公司债券(第一期)</t>
+          <t>东港投资发展集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ32" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK32" s="3"/>
       <c r="AL32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM32" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AN32" s="3" t="inlineStr">
@@ -7544,37 +7548,37 @@
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP32" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AQ32" s="3" t="inlineStr">
         <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>园区开发运营</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR32" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>产业控股</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
       <c r="AU32" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AV32" s="3" t="inlineStr">
@@ -7584,7 +7588,7 @@
       </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX32" s="3" t="inlineStr">
@@ -7602,7 +7606,7 @@
     <row r="33" customHeight="true" ht="18.0">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>26东港投资PPN001</t>
+          <t>26渝保税MTN002</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -7612,62 +7616,62 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>032680497.IB</t>
+          <t>102683415.IB</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.50 ~ 2.20</t>
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>26东港02</t>
+          <t>26渝保税MTN001</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+2.00Y</t>
+          <t>4.58Y</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>1.8000</t>
+          <t>1.8396</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>--/1.7300</t>
+          <t>1.8650/1.8400</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>东港投资发展集团有限公司</t>
+          <t>重庆保税港区开发管理集团有限公司</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>B- 37.72</t>
+          <t>B- 36.36</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
@@ -7677,7 +7681,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 14:00</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -7691,44 +7695,46 @@
         </is>
       </c>
       <c r="U33" s="4" t="n">
-        <v>2.8667</v>
-      </c>
-      <c r="V33" s="3"/>
+        <v>2.65</v>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>1.25</v>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>1.84%~1.94%</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z33" s="3"/>
       <c r="AA33" s="3" t="inlineStr">
         <is>
-          <t>浙江省-舟山市</t>
+          <t>重庆市-两江新区</t>
         </is>
       </c>
       <c r="AB33" s="3" t="inlineStr">
         <is>
-          <t>发行人本期定向债务融资工具募集资金中,3.00亿元拟用于偿还21东港投资PPN001的本金[21东港投资PPN001]</t>
+          <t>发行人本期中期票据发行金额12亿元,全部用于偿还发行人本部债务融资工具本金[25渝保税SCP002]</t>
         </is>
       </c>
       <c r="AC33" s="3" t="inlineStr">
         <is>
-          <t>杭州银行股份有限公司,国泰海通证券股份有限公司</t>
+          <t>中国光大银行股份有限公司,重庆农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF33" s="3" t="inlineStr">
@@ -7743,12 +7749,12 @@
       </c>
       <c r="AH33" s="3" t="inlineStr">
         <is>
-          <t>东港投资发展集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>重庆保税港区开发管理集团有限公司2026年度第二期中期票据</t>
         </is>
       </c>
       <c r="AI33" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ33" s="3" t="inlineStr">
@@ -7774,12 +7780,12 @@
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP33" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ33" s="3" t="inlineStr">
@@ -7799,12 +7805,12 @@
       </c>
       <c r="AT33" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU33" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV33" s="3" t="inlineStr">
@@ -7814,7 +7820,7 @@
       </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX33" s="3" t="inlineStr">
@@ -7832,7 +7838,7 @@
     <row r="34" customHeight="true" ht="18.0">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>26渝保税MTN002</t>
+          <t>26万宝租赁MTN001</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -7842,62 +7848,62 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>102683415.IB</t>
+          <t>102683411.IB</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.20</t>
+          <t>1.70 ~ 2.30</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>26渝保税MTN001</t>
+          <t>26杭租02</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>4.58Y</t>
+          <t>2.96Y</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1.8396</t>
+          <t>1.8780</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>1.8650/1.8400</t>
+          <t>--/1.8500</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>重庆保税港区开发管理集团有限公司</t>
+          <t>广州工控万宝融资租赁有限公司</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t>B- 36.36</t>
+          <t>D+ 5.70</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
@@ -7907,7 +7913,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>08-27 14:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
@@ -7921,19 +7927,19 @@
         </is>
       </c>
       <c r="U34" s="4" t="n">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>1.25</v>
+        <v>7.0</v>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>7+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t>1.84%~1.94%</t>
+          <t>1.78%~1.88%</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
@@ -7944,17 +7950,17 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3" t="inlineStr">
         <is>
-          <t>重庆市-两江新区</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB34" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据发行金额12亿元,全部用于偿还发行人本部债务融资工具本金[25渝保税SCP002]</t>
+          <t>发行人本期中期票据基础发行规模为0亿元，发行规模上限为5亿元。本期中期票据募集资金拟全部用于偿还发行人本部有息债务</t>
         </is>
       </c>
       <c r="AC34" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,重庆农村商业银行股份有限公司</t>
+          <t>中国光大银行股份有限公司,东莞农村商业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD34" s="3"/>
@@ -7975,7 +7981,7 @@
       </c>
       <c r="AH34" s="3" t="inlineStr">
         <is>
-          <t>重庆保税港区开发管理集团有限公司2026年度第二期中期票据</t>
+          <t>广州工控万宝融资租赁有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI34" s="3" t="inlineStr">
@@ -7985,7 +7991,7 @@
       </c>
       <c r="AJ34" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AK34" s="3"/>
@@ -8006,7 +8012,7 @@
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP34" s="3" t="inlineStr">
@@ -8016,22 +8022,22 @@
       </c>
       <c r="AQ34" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT34" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU34" s="3" t="inlineStr">
@@ -8064,72 +8070,72 @@
     <row r="35" customHeight="true" ht="18.0">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>26万宝租赁MTN001</t>
+          <t>26舟交02</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>102683411.IB</t>
+          <t>245968.SH</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>26杭租02</t>
+          <t>26舟山交投MTN002</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>2.96Y</t>
+          <t>4.75Y</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>1.8780</t>
+          <t>1.8479</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t>--/1.8500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>广州工控万宝融资租赁有限公司</t>
+          <t>舟山交通投资集团有限公司</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t>D+ 5.70</t>
+          <t>C- 17.29</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
@@ -8139,7 +8145,7 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
@@ -8149,23 +8155,21 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U35" s="4" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="V35" s="4" t="n">
-        <v>7.0</v>
-      </c>
+        <v>4.48</v>
+      </c>
+      <c r="V35" s="3"/>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>7+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t>1.78%~1.88%</t>
+          <t>1.75%~1.85%</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
@@ -8176,23 +8180,23 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>浙江省-舟山市</t>
         </is>
       </c>
       <c r="AB35" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模为0亿元，发行规模上限为5亿元。本期中期票据募集资金拟全部用于偿还发行人本部有息债务</t>
+          <t>本期公司债券募集资金扣除发行费用后,发行人拟将6亿元用于偿还到期的公司债券本金[21舟交02]</t>
         </is>
       </c>
       <c r="AC35" s="3" t="inlineStr">
         <is>
-          <t>中国光大银行股份有限公司,东莞农村商业银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD35" s="3"/>
       <c r="AE35" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF35" s="3" t="inlineStr">
@@ -8202,12 +8206,12 @@
       </c>
       <c r="AG35" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH35" s="3" t="inlineStr">
         <is>
-          <t>广州工控万宝融资租赁有限公司2026年度第一期中期票据</t>
+          <t>舟山交通投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI35" s="3" t="inlineStr">
@@ -8217,53 +8221,57 @@
       </c>
       <c r="AJ35" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
-        </is>
-      </c>
-      <c r="AK35" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK35" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL35" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AM35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP35" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ35" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他交运基础设施</t>
         </is>
       </c>
       <c r="AT35" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="AU35" s="3" t="inlineStr">
@@ -8296,17 +8304,17 @@
     <row r="36" customHeight="true" ht="18.0">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>26舟交02</t>
+          <t>26建安投资MTN004B</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>08-27 19:00</t>
+          <t>08-28 18:00</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>245968.SH</t>
+          <t>102683443.IB</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -8315,53 +8323,53 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.70 ~ 2.40</t>
         </is>
       </c>
       <c r="H36" s="4" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>26舟山交投MTN002</t>
+          <t>21建安债01</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>4.75Y</t>
+          <t>4.97Y</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>1.8479</t>
+          <t>1.9958</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0000/1.9800</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>舟山交通投资集团有限公司</t>
+          <t>建安投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>C- 17.29</t>
+          <t>C+ 33.98</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -8371,7 +8379,7 @@
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
@@ -8385,17 +8393,19 @@
         </is>
       </c>
       <c r="U36" s="4" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="V36" s="3"/>
+        <v>4.5333</v>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>1.67</v>
+      </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t>1.75%~1.85%</t>
+          <t>1.86%~1.96%</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
@@ -8406,23 +8416,23 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
-          <t>浙江省-舟山市</t>
+          <t>安徽省-亳州市</t>
         </is>
       </c>
       <c r="AB36" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,发行人拟将6亿元用于偿还到期的公司债券本金[21舟交02]</t>
+          <t>本期中期票据注册额度30亿元,本期发行金额5亿元,拟用于偿还发行人到期的银行间债务融资工具。[23建安投资MTN004]</t>
         </is>
       </c>
       <c r="AC36" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,中国国际金融股份有限公司,中信建投证券股份有限公司</t>
+          <t>中信银行股份有限公司,徽商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD36" s="3"/>
       <c r="AE36" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF36" s="3" t="inlineStr">
@@ -8432,12 +8442,12 @@
       </c>
       <c r="AG36" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH36" s="3" t="inlineStr">
         <is>
-          <t>舟山交通投资集团有限公司2026年面向专业投资者公开发行公司债券(第二期)</t>
+          <t>建安投资控股集团有限公司2026年度第四期中期票据(品种二)</t>
         </is>
       </c>
       <c r="AI36" s="3" t="inlineStr">
@@ -8457,7 +8467,7 @@
       </c>
       <c r="AL36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM36" s="3" t="inlineStr">
@@ -8472,32 +8482,32 @@
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP36" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ36" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
         <is>
-          <t>其他交运基础设施</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT36" s="3" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU36" s="3" t="inlineStr">
@@ -8522,7 +8532,7 @@
       </c>
       <c r="AY36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AZ36" s="3"/>
@@ -8530,72 +8540,72 @@
     <row r="37" customHeight="true" ht="18.0">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>26建安投资MTN004B</t>
+          <t>26中建材集MTN003(科创债)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>08-28 18:00</t>
+          <t>08-27 18:00</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>102683443.IB</t>
+          <t>102683418.IB</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.40</t>
+          <t>1.47 ~ 1.67</t>
         </is>
       </c>
       <c r="H37" s="4" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>21建安债01</t>
+          <t>24中建材集MTN001A(科创票据)</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>4.97Y</t>
+          <t>2.95Y</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>1.9958</t>
+          <t>1.6733</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t>2.0000/1.9800</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>建安投资控股集团有限公司</t>
+          <t>中国建材集团有限公司</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.98</t>
+          <t>B- 39.11</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
@@ -8615,44 +8625,44 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U37" s="4" t="n">
-        <v>4.5333</v>
+        <v>1.0273</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>1.67</v>
+        <v>1.0</v>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>4+</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1.86%~1.96%</t>
+          <t>1.63%~1.73%</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z37" s="3"/>
       <c r="AA37" s="3" t="inlineStr">
         <is>
-          <t>安徽省-亳州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB37" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据注册额度30亿元,本期发行金额5亿元,拟用于偿还发行人到期的银行间债务融资工具。[23建安投资MTN004]</t>
+          <t>本期债务融资工具发行规模为11亿元,募集资金用于偿还有息债务；本期科技创新债券的募集资金穿透实际用于发行人科技创新业务及主营业务新材料核心板块,主要投向新材料领域项下玻璃纤维、石膏板、风电叶片等的研发设备购置、核心生产装备升级改造及核心物料采购等</t>
         </is>
       </c>
       <c r="AC37" s="3" t="inlineStr">
         <is>
-          <t>中信银行股份有限公司,徽商银行股份有限公司</t>
+          <t>华夏银行股份有限公司,兴业银行股份有限公司</t>
         </is>
       </c>
       <c r="AD37" s="3"/>
@@ -8663,7 +8673,7 @@
       </c>
       <c r="AF37" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>中央国有企业</t>
         </is>
       </c>
       <c r="AG37" s="3" t="inlineStr">
@@ -8673,7 +8683,7 @@
       </c>
       <c r="AH37" s="3" t="inlineStr">
         <is>
-          <t>建安投资控股集团有限公司2026年度第四期中期票据(品种二)</t>
+          <t>中国建材集团有限公司2026年度第三期科技创新债券</t>
         </is>
       </c>
       <c r="AI37" s="3" t="inlineStr">
@@ -8683,17 +8693,13 @@
       </c>
       <c r="AJ37" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK37" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-28</t>
+        </is>
+      </c>
+      <c r="AK37" s="3"/>
       <c r="AL37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM37" s="3" t="inlineStr">
@@ -8703,37 +8709,37 @@
       </c>
       <c r="AN37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP37" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ37" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>建材制造</t>
         </is>
       </c>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>综合建材</t>
         </is>
       </c>
       <c r="AT37" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>水泥制造</t>
         </is>
       </c>
       <c r="AU37" s="3" t="inlineStr">
@@ -8758,7 +8764,7 @@
       </c>
       <c r="AY37" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="AZ37" s="3"/>
@@ -8766,17 +8772,17 @@
     <row r="38" customHeight="true" ht="18.0">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>26中建材集MTN003(科创债)</t>
+          <t>26医产K1</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>102683418.IB</t>
+          <t>520443.SZ</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
@@ -8785,53 +8791,53 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>1.47 ~ 1.67</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>24中建材集MTN001A(科创票据)</t>
+          <t>26君实生物MTN003(科创债)</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>2.95Y</t>
+          <t>2.98Y</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>1.6733</t>
+          <t>2.7236</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.7100</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>中国建材集团有限公司</t>
+          <t>四川生物医药产业集团有限责任公司</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>B- 39.11</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -8841,7 +8847,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
@@ -8851,121 +8857,111 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U38" s="4" t="n">
-        <v>1.0273</v>
-      </c>
-      <c r="V38" s="4" t="n">
-        <v>1.0</v>
-      </c>
+        <v>2.67</v>
+      </c>
+      <c r="V38" s="3"/>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t>4+</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t>1.63%~1.73%</t>
-        </is>
-      </c>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X38" s="3"/>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z38" s="3"/>
       <c r="AA38" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>四川省-成都市</t>
         </is>
       </c>
       <c r="AB38" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行规模为11亿元,募集资金用于偿还有息债务；本期科技创新债券的募集资金穿透实际用于发行人科技创新业务及主营业务新材料核心板块,主要投向新材料领域项下玻璃纤维、石膏板、风电叶片等的研发设备购置、核心生产装备升级改造及核心物料采购等</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟将不低于2.10亿元用于股权投资;不低于0.71亿元用于认购基金份额;剩余部分用于偿还有息债务。</t>
         </is>
       </c>
       <c r="AC38" s="3" t="inlineStr">
         <is>
-          <t>华夏银行股份有限公司,兴业银行股份有限公司</t>
+          <t>中国国际金融股份有限公司</t>
         </is>
       </c>
       <c r="AD38" s="3"/>
       <c r="AE38" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF38" s="3" t="inlineStr">
         <is>
-          <t>中央国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG38" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH38" s="3" t="inlineStr">
         <is>
-          <t>中国建材集团有限公司2026年度第三期科技创新债券</t>
+          <t>四川生物医药产业集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)(用于生物医药)</t>
         </is>
       </c>
       <c r="AI38" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ38" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="AM38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>产业</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AP38" s="3"/>
       <c r="AQ38" s="3" t="inlineStr">
         <is>
-          <t>建材制造</t>
+          <t>医药制造</t>
         </is>
       </c>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
         <is>
-          <t>综合建材</t>
+          <t>药品制造</t>
         </is>
       </c>
       <c r="AT38" s="3" t="inlineStr">
         <is>
-          <t>水泥制造</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU38" s="3" t="inlineStr">
@@ -8998,104 +8994,108 @@
     <row r="39" customHeight="true" ht="18.0">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>26医产K1</t>
+          <t>26北仑现代PPN001</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>08-27 19:00</t>
+          <t>08-27 18:00</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>520443.SZ</t>
+          <t>032680502.IB</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+2</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>1.60 ~ 2.60</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H39" s="4" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>24宁现02</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>226D+2.00Y</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>1.5501</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>宁波市北仑区现代服务业发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>C 28.33</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>08-27 09:00</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t>26君实生物MTN003(科创债)</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>2.98Y</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t>2.7236</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t>--/2.7100</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>四川生物医药产业集团有限责任公司</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t>E 0.00</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="R39" s="3" t="inlineStr">
-        <is>
-          <t>08-27 15:00</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="U39" s="4" t="n">
-        <v>2.67</v>
+        <v>3.35</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X39" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>1.71%~1.81%</t>
+        </is>
+      </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
           <t>AA+</t>
@@ -9104,23 +9104,23 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3" t="inlineStr">
         <is>
-          <t>四川省-成都市</t>
+          <t>浙江省-宁波市</t>
         </is>
       </c>
       <c r="AB39" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟将不低于2.10亿元用于股权投资;不低于0.71亿元用于认购基金份额;剩余部分用于偿还有息债务。</t>
+          <t>发行人本次债务融资工具募集资金拟用于偿还23北仑现代PPN001债券本金；发行人已通过银行借款偿还到期的23北仑现代PPN001，本期募集资金用途用于偿还该笔银行专项借款[23北仑现代PPN001]</t>
         </is>
       </c>
       <c r="AC39" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司</t>
+          <t>宁波银行股份有限公司,杭州银行股份有限公司,兴业银行股份有限公司,徽商银行股份有限公司,中信银行股份有限公司,北京银行股份有限公司</t>
         </is>
       </c>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>定向工具(PPN)</t>
         </is>
       </c>
       <c r="AF39" s="3" t="inlineStr">
@@ -9130,12 +9130,12 @@
       </c>
       <c r="AG39" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH39" s="3" t="inlineStr">
         <is>
-          <t>四川生物医药产业集团有限责任公司2026年面向专业投资者非公开发行科技创新公司债券(第一期)(用于生物医药)</t>
+          <t>宁波市北仑区现代服务业发展集团有限公司2026年度第一期定向债务融资工具</t>
         </is>
       </c>
       <c r="AI39" s="3" t="inlineStr">
@@ -9145,13 +9145,13 @@
       </c>
       <c r="AJ39" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
+          <t>2031-08-28</t>
         </is>
       </c>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AM39" s="3" t="inlineStr">
@@ -9161,28 +9161,32 @@
       </c>
       <c r="AN39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP39" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
       <c r="AQ39" s="3" t="inlineStr">
         <is>
-          <t>医药制造</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">
         <is>
-          <t>药品制造</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT39" s="3" t="inlineStr">
@@ -9192,7 +9196,7 @@
       </c>
       <c r="AU39" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2029-08-28</t>
         </is>
       </c>
       <c r="AV39" s="3" t="inlineStr">
@@ -9202,7 +9206,7 @@
       </c>
       <c r="AW39" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX39" s="3" t="inlineStr">
@@ -9220,72 +9224,72 @@
     <row r="40" customHeight="true" ht="18.0">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>26北仑现代PPN001</t>
+          <t>26太新Y7</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>08-27 18:00</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>032680502.IB</t>
+          <t>245995.SH</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>3+2</t>
+          <t>7+N</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>2.00 ~ 3.00</t>
         </is>
       </c>
       <c r="H40" s="4" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>24宁现02</t>
+          <t>26太新Y6</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>226D+2.00Y</t>
+          <t>6.98Y+N</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1.5501</t>
+          <t>2.2233</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/2.2150</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>宁波市北仑区现代服务业发展集团有限公司</t>
+          <t>无锡市太湖新城发展集团有限公司</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>C 28.33</t>
+          <t>B- 35.06</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -9295,7 +9299,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
@@ -9305,48 +9309,48 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="U40" s="4" t="n">
-        <v>3.35</v>
+        <v>2.19</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>4-</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t>1.71%~1.81%</t>
+          <t>2.37%~2.47%</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3" t="inlineStr">
         <is>
-          <t>浙江省-宁波市</t>
+          <t>江苏省-无锡市</t>
         </is>
       </c>
       <c r="AB40" s="3" t="inlineStr">
         <is>
-          <t>发行人本次债务融资工具募集资金拟用于偿还23北仑现代PPN001债券本金；发行人已通过银行借款偿还到期的23北仑现代PPN001，本期募集资金用途用于偿还该笔银行专项借款[23北仑现代PPN001]</t>
+          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券的本金[24太新Y1]</t>
         </is>
       </c>
       <c r="AC40" s="3" t="inlineStr">
         <is>
-          <t>宁波银行股份有限公司,杭州银行股份有限公司,兴业银行股份有限公司,徽商银行股份有限公司,中信银行股份有限公司,北京银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信证券股份有限公司,国联民生证券承销保荐有限公司,东吴证券股份有限公司</t>
         </is>
       </c>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3" t="inlineStr">
         <is>
-          <t>定向工具(PPN)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF40" s="3" t="inlineStr">
@@ -9356,28 +9360,28 @@
       </c>
       <c r="AG40" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH40" s="3" t="inlineStr">
         <is>
-          <t>宁波市北仑区现代服务业发展集团有限公司2026年度第一期定向债务融资工具</t>
+          <t>无锡市太湖新城发展集团有限公司2026年面向专业投资者公开发行可续期公司债券(第四期)</t>
         </is>
       </c>
       <c r="AI40" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ40" s="3" t="inlineStr">
         <is>
-          <t>2031-08-28</t>
+          <t>2033-09-01</t>
         </is>
       </c>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t/>
         </is>
       </c>
       <c r="AM40" s="3" t="inlineStr">
@@ -9387,7 +9391,7 @@
       </c>
       <c r="AN40" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AO40" s="3" t="inlineStr">
@@ -9407,22 +9411,22 @@
       </c>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT40" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU40" s="3" t="inlineStr">
         <is>
-          <t>2029-08-28</t>
+          <t/>
         </is>
       </c>
       <c r="AV40" s="3" t="inlineStr">
@@ -9432,7 +9436,7 @@
       </c>
       <c r="AW40" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX40" s="3" t="inlineStr">
@@ -9450,7 +9454,7 @@
     <row r="41" customHeight="true" ht="18.0">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>26太新Y7</t>
+          <t>26新乡Y1</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -9460,62 +9464,62 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>245995.SH</t>
+          <t>283836.SH</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>7+N</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>9.0</v>
+        <v>4.0</v>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.60 ~ 2.60</t>
         </is>
       </c>
       <c r="H41" s="4" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>26太新Y6</t>
+          <t>26新乡投资PPN002</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>6.98Y+N</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>2.2233</t>
+          <t>1.8637</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>--/2.2150</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司</t>
+          <t>新乡投资集团有限公司</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t>B- 35.06</t>
+          <t>C 25.13</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
@@ -9535,23 +9539,19 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="U41" s="4" t="n">
-        <v>2.19</v>
+        <v>3.5</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>4-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t>2.37%~2.47%</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X41" s="3"/>
       <c r="Y41" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -9560,17 +9560,17 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
-          <t>江苏省-无锡市</t>
+          <t>河南省-新乡市</t>
         </is>
       </c>
       <c r="AB41" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后,拟全部用于偿还到期公司债券的本金[24太新Y1]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还即将到期公司债券本金。[23 新乡03]</t>
         </is>
       </c>
       <c r="AC41" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,国泰海通证券股份有限公司,中信证券股份有限公司,国联民生证券承销保荐有限公司,东吴证券股份有限公司</t>
+          <t>华泰联合证券有限责任公司,国联民生证券承销保荐有限公司</t>
         </is>
       </c>
       <c r="AD41" s="3"/>
@@ -9591,70 +9591,70 @@
       </c>
       <c r="AH41" s="3" t="inlineStr">
         <is>
-          <t>无锡市太湖新城发展集团有限公司2026年面向专业投资者公开发行可续期公司债券(第四期)</t>
+          <t>新乡投资集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ41" s="3" t="inlineStr">
         <is>
-          <t>2033-09-01</t>
+          <t>2029-08-31</t>
         </is>
       </c>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr">
+        <is>
+          <t>综合</t>
+        </is>
+      </c>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>国资经营</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>房屋建设</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM41" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AO41" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ41" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR41" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV41" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -9667,7 +9667,7 @@
       </c>
       <c r="AX41" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY41" s="3" t="inlineStr">
@@ -17084,7 +17084,7 @@
     <row r="74" customHeight="true" ht="18.0">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>26合高02</t>
+          <t>26济旅04</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>283816.SH</t>
+          <t>283750.SH</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E74" s="4" t="n">
@@ -17110,46 +17110,46 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>1.90 ~ 2.70</t>
         </is>
       </c>
       <c r="H74" s="4" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="I74" s="3"/>
       <c r="J74" s="3" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>26合高01</t>
+          <t>26济旅03</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
-          <t>2.92Y</t>
+          <t>4.64Y</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>1.7740</t>
+          <t>2.1766</t>
         </is>
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>合肥高新控股集团有限公司</t>
+          <t>济南文旅发展集团有限公司</t>
         </is>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
-          <t>A- 64.62</t>
+          <t>D+ 6.25</t>
         </is>
       </c>
       <c r="Q74" s="3" t="inlineStr">
@@ -17159,7 +17159,7 @@
       </c>
       <c r="R74" s="3" t="inlineStr">
         <is>
-          <t>08-27 16:00</t>
+          <t>08-27 15:00</t>
         </is>
       </c>
       <c r="S74" s="3" t="inlineStr">
@@ -17172,16 +17172,18 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U74" s="3"/>
+      <c r="U74" s="4" t="n">
+        <v>2.4</v>
+      </c>
       <c r="V74" s="3"/>
       <c r="W74" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X74" s="3" t="inlineStr">
         <is>
-          <t>1.77%~1.87%</t>
+          <t>2.24%~2.34%</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
@@ -17192,17 +17194,17 @@
       <c r="Z74" s="3"/>
       <c r="AA74" s="3" t="inlineStr">
         <is>
-          <t>安徽省-合肥市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB74" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金总额不超过5亿元。扣除发行费用后拟全部用于偿还到期公司债券本金[23 合高K1]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务,包括公司债券本金和其他有息债务[23济旅02]</t>
         </is>
       </c>
       <c r="AC74" s="3" t="inlineStr">
         <is>
-          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD74" s="3"/>
@@ -17223,7 +17225,7 @@
       </c>
       <c r="AH74" s="3" t="inlineStr">
         <is>
-          <t>合肥高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>济南文旅发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
         </is>
       </c>
       <c r="AI74" s="3" t="inlineStr">
@@ -17233,13 +17235,17 @@
       </c>
       <c r="AJ74" s="3" t="inlineStr">
         <is>
-          <t>2029-08-31</t>
-        </is>
-      </c>
-      <c r="AK74" s="3"/>
+          <t>2031-08-31</t>
+        </is>
+      </c>
+      <c r="AK74" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t/>
         </is>
       </c>
       <c r="AM74" s="3" t="inlineStr">
@@ -17259,7 +17265,7 @@
       </c>
       <c r="AP74" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ74" s="3" t="inlineStr">
@@ -17269,17 +17275,17 @@
       </c>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
         <is>
-          <t>园区开发运营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT74" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU74" s="3" t="inlineStr">
@@ -17312,72 +17318,72 @@
     <row r="75" customHeight="true" ht="18.0">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>26济旅04</t>
+          <t>26湖南银行小微债01</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>08-27 19:00</t>
+          <t>08-27 17:30</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>283750.SH</t>
+          <t>2620005.IB</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E75" s="4" t="n">
-        <v>5.0</v>
+        <v>60.0</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>5.0</v>
+        <v>60.0</v>
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>1.90 ~ 2.70</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H75" s="4" t="n">
-        <v>2.15</v>
+        <v>1.59</v>
       </c>
       <c r="I75" s="3"/>
       <c r="J75" s="3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t>26济旅03</t>
+          <t>26湖南银行债01</t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>4.64Y</t>
+          <t>2.93Y</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>2.1766</t>
+          <t>1.5976</t>
         </is>
       </c>
       <c r="N75" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6100/1.6000</t>
         </is>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>济南文旅发展集团有限公司</t>
+          <t>湖南银行股份有限公司</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.25</t>
+          <t>A- 67.73</t>
         </is>
       </c>
       <c r="Q75" s="3" t="inlineStr">
@@ -17387,7 +17393,7 @@
       </c>
       <c r="R75" s="3" t="inlineStr">
         <is>
-          <t>08-27 15:00</t>
+          <t>08-27 09:00</t>
         </is>
       </c>
       <c r="S75" s="3" t="inlineStr">
@@ -17400,45 +17406,47 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="U75" s="4" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="U75" s="3"/>
       <c r="V75" s="3"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>2.24%~2.34%</t>
+          <t>1.56%~1.66%</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
-        </is>
-      </c>
-      <c r="Z75" s="3"/>
+          <t>AAA</t>
+        </is>
+      </c>
+      <c r="Z75" s="3" t="inlineStr">
+        <is>
+          <t>AAA</t>
+        </is>
+      </c>
       <c r="AA75" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>湖南省-长沙市</t>
         </is>
       </c>
       <c r="AB75" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟全部用于偿还有息债务,包括公司债券本金和其他有息债务[23济旅02]</t>
+          <t xml:space="preserve">本期债券的募集资金将依据适用法律和监管部门的批准，专项用于发放小型微型企业贷款，加大对小型微型企业信贷支持力度，推动小型微型企业业务稳健、健康发展。 </t>
         </is>
       </c>
       <c r="AC75" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,兴业银行股份有限公司,华夏银行股份有限公司,恒丰银行股份有限公司,申万宏源证券有限公司,国开证券股份有限公司</t>
         </is>
       </c>
       <c r="AD75" s="3"/>
       <c r="AE75" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF75" s="3" t="inlineStr">
@@ -17448,37 +17456,33 @@
       </c>
       <c r="AG75" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH75" s="3" t="inlineStr">
         <is>
-          <t>济南文旅发展集团有限公司2026年面向专业投资者非公开发行公司债券(第三期)</t>
+          <t>湖南银行股份有限公司2026年第一期小型微型企业贷款专项金融债券</t>
         </is>
       </c>
       <c r="AI75" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ75" s="3" t="inlineStr">
         <is>
-          <t>2031-08-31</t>
-        </is>
-      </c>
-      <c r="AK75" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-08-31</t>
+        </is>
+      </c>
+      <c r="AK75" s="3"/>
       <c r="AL75" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="AM75" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="AN75" s="3" t="inlineStr">
@@ -17488,32 +17492,32 @@
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP75" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AQ75" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">
         <is>
-          <t>其他基础设施投融资建设</t>
+          <t>城商行</t>
         </is>
       </c>
       <c r="AT75" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU75" s="3" t="inlineStr">
@@ -17546,17 +17550,17 @@
     <row r="76" customHeight="true" ht="18.0">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>26湖南银行小微债01</t>
+          <t>26合高02</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>08-27 17:30</t>
+          <t>08-27 19:00</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>2620005.IB</t>
+          <t>283816.SH</t>
         </is>
       </c>
       <c r="D76" s="3" t="inlineStr">
@@ -17565,53 +17569,53 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>60.0</v>
+        <v>5.0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>60.0</v>
+        <v>5.0</v>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H76" s="4" t="n">
-        <v>1.59</v>
+        <v>1.72</v>
       </c>
       <c r="I76" s="3"/>
       <c r="J76" s="3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>26湖南银行债01</t>
+          <t>26合高01</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2.93Y</t>
+          <t>2.92Y</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>1.5976</t>
+          <t>1.7740</t>
         </is>
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>1.6100/1.6000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>湖南银行股份有限公司</t>
+          <t>合肥高新控股集团有限公司</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
-          <t>A- 67.73</t>
+          <t>A- 64.62</t>
         </is>
       </c>
       <c r="Q76" s="3" t="inlineStr">
@@ -17621,7 +17625,7 @@
       </c>
       <c r="R76" s="3" t="inlineStr">
         <is>
-          <t>08-27 09:00</t>
+          <t>08-27 16:00</t>
         </is>
       </c>
       <c r="S76" s="3" t="inlineStr">
@@ -17643,38 +17647,34 @@
       </c>
       <c r="X76" s="3" t="inlineStr">
         <is>
-          <t>1.56%~1.66%</t>
+          <t>1.77%~1.87%</t>
         </is>
       </c>
       <c r="Y76" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
-        </is>
-      </c>
-      <c r="Z76" s="3" t="inlineStr">
-        <is>
-          <t>AAA</t>
-        </is>
-      </c>
+          <t>AA+</t>
+        </is>
+      </c>
+      <c r="Z76" s="3"/>
       <c r="AA76" s="3" t="inlineStr">
         <is>
-          <t>湖南省-长沙市</t>
+          <t>安徽省-合肥市</t>
         </is>
       </c>
       <c r="AB76" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本期债券的募集资金将依据适用法律和监管部门的批准，专项用于发放小型微型企业贷款，加大对小型微型企业信贷支持力度，推动小型微型企业业务稳健、健康发展。 </t>
+          <t>本期债券的募集资金总额不超过5亿元。扣除发行费用后拟全部用于偿还到期公司债券本金[23 合高K1]</t>
         </is>
       </c>
       <c r="AC76" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中国国际金融股份有限公司,中信证券股份有限公司,中信建投证券股份有限公司,兴业银行股份有限公司,华夏银行股份有限公司,恒丰银行股份有限公司,申万宏源证券有限公司,国开证券股份有限公司</t>
+          <t>中信证券股份有限公司,中国国际金融股份有限公司,中信建投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD76" s="3"/>
       <c r="AE76" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF76" s="3" t="inlineStr">
@@ -17684,17 +17684,17 @@
       </c>
       <c r="AG76" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH76" s="3" t="inlineStr">
         <is>
-          <t>湖南银行股份有限公司2026年第一期小型微型企业贷款专项金融债券</t>
+          <t>合肥高新控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI76" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ76" s="3" t="inlineStr">
@@ -17705,12 +17705,12 @@
       <c r="AK76" s="3"/>
       <c r="AL76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AM76" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="AN76" s="3" t="inlineStr">
@@ -17720,32 +17720,32 @@
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP76" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ76" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
         <is>
-          <t>城商行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT76" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU76" s="3" t="inlineStr">
